--- a/mod_project/data_tables/skills.xlsx
+++ b/mod_project/data_tables/skills.xlsx
@@ -547,13 +547,13 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Attract single-target attacks to user with high speed turn recovery.</t>
+          <t>Attract single-target attacks to user. High turn speed recovery.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Turns: 3 (L1) -&gt; 4 (L2) -&gt; 5 (L3) -&gt; 6 (L4) -&gt; 7 (L5 Max).
-Speed: +50% -&gt; +63% -&gt; +76% -&gt; +89% -&gt; +100%. TP: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5.</t>
+          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-L5)    |    Speed: +50% -&gt; +100%
+TP Cost: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -651,13 +651,13 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Raise party physical ATK &amp; replace debuffs. Usable out of battle.</t>
+          <t>Raise party physical ATK &amp; cleanse debuffs. Usable out of battle.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ATK: +8% (L1) -&gt; +10% (L2) -&gt; +12% (L3) -&gt; +14% (L4) -&gt; +18% (L5 Max).
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8. TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13.</t>
+          <t>ATK: +8% -&gt; +10% -&gt; +12% -&gt; +14% -&gt; +18% (L1-L5 Max)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8    |    TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -711,13 +711,13 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Short-range skill. Strike one enemy for 125% ATK (+8%/Lv, Max 200%).</t>
+          <t>Short-range strike. Boosted accuracy (+20% to +38%). Delay: 0.80x.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Hit Rate: +20% (+2%/Lv, Max +38%). Action delay: 0.80x~0.90x.
-TP Cost: 5 (Lv1) -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 (Max).</t>
+          <t>ATK: 125% (L1) -&gt; 133 -&gt; 141 -&gt; 150 -&gt; 158 -&gt; 166 -&gt; 175 -&gt; 183 -&gt; 191 -&gt; 200% (L10)
+TP Cost: 5 (L1) -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 (Max)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -864,8 +864,8 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>DEF: +20% (L1) -&gt; +27% (L2) -&gt; +35% (L3) -&gt; +42% (L4) -&gt; +50% (L5 Max).
-ATK: -11% -&gt; -14% -&gt; -18% -&gt; -21% -&gt; -25%. TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16.</t>
+          <t>DEF: +20% -&gt; +27% -&gt; +35% -&gt; +42% -&gt; +50% (L1-L5 Max)
+ATK: -11% -&gt; -25%    |    TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1452,8 +1452,8 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Turns: 4 (L1) -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L5 Max). TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 20 -&gt; 24.
-Guard chance: 30%~60% on hit. Requires 1H weapon &amp; shield.</t>
+          <t>Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-L5)    |    Guard chance: 30% to 60%
+TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 20 -&gt; 24    |    Requires 1H weapon &amp; shield</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1512,8 +1512,8 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Turns: 3 (L1) -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L5 Max). TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22.
-May break on consecutive blocks. Fast recovery (1.30x speed).</t>
+          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-L5)    |    Recovery Speed: 1.30x
+TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22    |    May break on repeat blocks</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">

--- a/mod_project/data_tables/skills.xlsx
+++ b/mod_project/data_tables/skills.xlsx
@@ -547,12 +547,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Attract single-target attacks to user. High turn speed recovery.</t>
+          <t>Attract single-target attacks.    |    Fast turn recovery.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-L5)    |    Speed: +50% -&gt; +100%
+          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5)    |    Speed: +50% -&gt; +100%
 TP Cost: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5</t>
         </is>
       </c>
@@ -656,7 +656,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ATK: +8% -&gt; +10% -&gt; +12% -&gt; +14% -&gt; +18% (L1-L5 Max)
+          <t>ATK: +8% -&gt; +10% -&gt; +12% -&gt; +14% -&gt; +18% (L1-5 Max)
 Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8    |    TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13</t>
         </is>
       </c>
@@ -711,13 +711,13 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Short-range strike. Boosted accuracy (+20% to +38%). Delay: 0.80x.</t>
+          <t>Short-range strike.    |    Hit Rate: +20% (Lv1) -&gt; +38% (Max)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ATK: 125% (L1) -&gt; 133 -&gt; 141 -&gt; 150 -&gt; 158 -&gt; 166 -&gt; 175 -&gt; 183 -&gt; 191 -&gt; 200% (L10)
-TP Cost: 5 (L1) -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 (Max)</t>
+          <t>ATK (L1-10): 125% -&gt; 133 -&gt; 141 -&gt; 150 -&gt; 158 -&gt; 166 -&gt; 175 -&gt; 183 -&gt; 191 -&gt; 200%
+TP Cost: 5 -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28  (Lv1 to Max)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>DEF: +20% -&gt; +27% -&gt; +35% -&gt; +42% -&gt; +50% (L1-L5 Max)
+          <t>DEF: +20% -&gt; +27% -&gt; +35% -&gt; +42% -&gt; +50% (L1-5 Max)
 ATK: -11% -&gt; -25%    |    TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>

--- a/mod_project/data_tables/skills.xlsx
+++ b/mod_project/data_tables/skills.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5)    |    Speed: +50% -&gt; +100%
+          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5)    |    Speed: +50% -&gt; +100% (+12.5%/Lv)
 TP Cost: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5</t>
         </is>
       </c>
@@ -711,7 +711,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Short-range strike.    |    Hit Rate: +20% (Lv1) -&gt; +38% (Max)</t>
+          <t>Short-range strike.    |    Hit Rate: +20% -&gt; +38% (+2%/Lv)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -865,7 +865,7 @@
       <c r="J8" t="inlineStr">
         <is>
           <t>DEF: +20% -&gt; +27% -&gt; +35% -&gt; +42% -&gt; +50% (L1-5 Max)
-ATK: -11% -&gt; -25%    |    TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
+ATK: -11% -&gt; -25% (-3.5%/Lv)    |    TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-L5)    |    Guard chance: 30% to 60%
+          <t>Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5)    |    Guard: 30% -&gt; 60% (+7.5%/Lv)
 TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 20 -&gt; 24    |    Requires 1H weapon &amp; shield</t>
         </is>
       </c>

--- a/mod_project/data_tables/skills.xlsx
+++ b/mod_project/data_tables/skills.xlsx
@@ -563,7 +563,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Fast turn recovery (+50% to +100% action delay).</t>
+          <t>Fast turn recovery.</t>
         </is>
       </c>
     </row>
@@ -605,9 +605,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Attract all enemies' attacks to user with high speed turn recovery.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5)    |    Speed: +40% -&gt; +80% (+10%/Lv)
+TP Cost: 3 -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 11</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>AoE provoke.</t>
         </is>
       </c>
     </row>
@@ -667,7 +683,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Best party physical buff. Replaces active ATK debuffs.</t>
+          <t>Best party physical buff.</t>
         </is>
       </c>
     </row>
@@ -727,7 +743,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Short weapon only. Solid accuracy scaling.</t>
+          <t>Short weapon only.</t>
         </is>
       </c>
     </row>
@@ -769,9 +785,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Short-range strike to one enemy. May cancel enemy active buffs.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Dispel Chance: 30% -&gt; 60% (+7.5%/Lv)    |    Levels: L1-5
+TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Cancels boss buffs.</t>
         </is>
       </c>
     </row>
@@ -813,9 +845,25 @@
 Time until next turn DOWN TP Cost UP DEF decrease UP</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Greatly boost own physical ATK at the cost of lowering own DEF.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ATK: +25% -&gt; +35% -&gt; +45% -&gt; +55% -&gt; +65% (L1-5)    |    DEF: -15% -&gt; -35%
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8    |    TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High risk buff.</t>
         </is>
       </c>
     </row>
@@ -875,7 +923,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Lasts 4~8 turns. 1.25x~1.77x speed. ATK debuff is removable.</t>
+          <t>Defensive stance.</t>
         </is>
       </c>
     </row>
@@ -917,9 +965,25 @@
 Stun rate UP TP Cost UP</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Shield skill. Deal bash damage to one enemy. May stun.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ATK: 110% -&gt; 120% -&gt; 130% -&gt; 140% -&gt; 150% (L1-5)    |    Stun: 20% -&gt; 40%
+TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14    |    Requires equipped shield</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Shield bash stun.</t>
         </is>
       </c>
     </row>
@@ -1049,9 +1113,25 @@
 Instakill rate UP TP Cost UP</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Katana skill. Deal slash damage to an enemy row. May instakill.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ATK: 115% -&gt; 130% -&gt; 145% -&gt; 160% -&gt; 175% (L1-5)    |    Instakill: 10% -&gt; 25%
+TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 28</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Row instakill slice.</t>
         </is>
       </c>
     </row>
@@ -1093,9 +1173,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Katana skill. Deal defense-piercing damage and lower target DEF.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ATK: 120% -&gt; 135% -&gt; 150% -&gt; 165% -&gt; 180% (L1-5)    |    DEF Debuff: -15% -&gt; -30%
+TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20    |    Bypasses enemy armor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Pierces armor.</t>
         </is>
       </c>
     </row>
@@ -1137,9 +1233,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Katana skill. Strike an enemy row with fierce slashing blades.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ATK: 130% -&gt; 145% -&gt; 160% -&gt; 175% -&gt; 190% (L1-5)
+TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Katana row slash.</t>
         </is>
       </c>
     </row>
@@ -1181,9 +1293,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Katana skill. Strike 3 times against one living enemy.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ATK: 70% -&gt; 80% -&gt; 90% -&gt; 100% -&gt; 110% per hit (3 hits total)
+TP Cost: 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30    |    Target must be living (not undead)</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>3 hit katana strike.</t>
         </is>
       </c>
     </row>
@@ -1225,9 +1353,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Short-range strike to one enemy. Absorb a portion of damage as HP.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ATK: 110% -&gt; 125% -&gt; 140% -&gt; 155% -&gt; 170% (L1-5)
+HP Absorb: 20% -&gt; 30% -&gt; 40% -&gt; 50% -&gt; 60%    |    TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Life drain strike.</t>
         </is>
       </c>
     </row>
@@ -1269,9 +1413,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Short-range strike to one enemy. Absorb a portion of damage as TP.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ATK: 100% -&gt; 110% -&gt; 120% -&gt; 130% -&gt; 140% (L1-5)
+TP Absorb: 5% -&gt; 8% -&gt; 11% -&gt; 14% -&gt; 18%    |    TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>TP drain strike.</t>
         </is>
       </c>
     </row>
@@ -1313,9 +1473,25 @@
 Time until next turn DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Short-range strike dealing mid-range water damage. May freeze.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ATK: 120% -&gt; 135% -&gt; 150% -&gt; 165% -&gt; 180% (L1-5)    |    Freeze: 20% -&gt; 40%
+TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Water slash.</t>
         </is>
       </c>
     </row>
@@ -1357,9 +1533,25 @@
 Time until next turn DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Axe skill. Strike one enemy with earth damage. May petrify.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ATK: 130% -&gt; 150% -&gt; 170% -&gt; 190% -&gt; 210% (L1-5)    |    Petrify: 15% -&gt; 30%
+TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Earth axe hit.</t>
         </is>
       </c>
     </row>
@@ -1401,9 +1593,25 @@
 Time until next turn DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Axe skill. Strike target and the next immediate enemy in turn order.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ATK: 140% -&gt; 160% -&gt; 180% -&gt; 200% -&gt; 220% (L1-5)
+TP Cost: 16 -&gt; 19 -&gt; 22 -&gt; 25 -&gt; 28    |    Hits 2 sequential turn targets</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Sequential targets.</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1671,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Can evade while covering. May attract counters.</t>
+          <t>Protects allies.</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1720,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-L5)    |    Recovery Speed: 1.30x
+          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5)    |    Recovery Speed: 1.30x
 TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22    |    May break on repeat blocks</t>
         </is>
       </c>
@@ -1523,7 +1731,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Blocks single/AoE physical damage toward user.</t>
+          <t>Weapon block.</t>
         </is>
       </c>
     </row>
@@ -1565,9 +1773,25 @@
 Time until next turn DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Sword and lance skill. Strike one enemy. Effective vs. Unholy foes.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ATK: 140% -&gt; 155% -&gt; 170% -&gt; 185% -&gt; 200% (L1-5)    |    Unholy Bonus: 1.50x
+TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Bonus vs unholy.</t>
         </is>
       </c>
     </row>
@@ -1609,9 +1833,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Shield skill. Erect a physical barrier mitigating party damage once.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Damage Reduction: -30% -&gt; -50% (-5%/Lv)    |    Levels: L1-5
+TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26    |    Requires shield</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Party physical shield.</t>
         </is>
       </c>
     </row>
@@ -1653,9 +1893,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Shield skill. Erect a magic barrier mitigating party magic damage once.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Magic Reduction: -30% -&gt; -50% (-5%/Lv)    |    Levels: L1-5
+TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26    |    Requires shield</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Party magic shield.</t>
         </is>
       </c>
     </row>
@@ -1697,9 +1953,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Short-range skill. Deal lightning damage to an enemy row. May paralyze.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ATK: 110% -&gt; 125% -&gt; 140% -&gt; 155% -&gt; 170% (L1-5)    |    Paralysis: 20% -&gt; 40%
+TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Row lightning.</t>
         </is>
       </c>
     </row>
@@ -1741,9 +2013,25 @@
 Time until next turn DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Lance skill. Strike one enemy with wind damage. May silence.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ATK: 125% -&gt; 140% -&gt; 155% -&gt; 170% -&gt; 185% (L1-5)    |    Silence: 20% -&gt; 40%
+TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Wind lance hit.</t>
         </is>
       </c>
     </row>
@@ -1785,9 +2073,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Lance skill. Rapidly strike random enemies 3 to 5 times.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ATK: 65% -&gt; 75% -&gt; 85% -&gt; 95% -&gt; 105% per hit (L1-5)
+TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 28    |    Heavy Lance bonus: +20% dmg</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Multi-hit lance skill.</t>
         </is>
       </c>
     </row>
@@ -1873,9 +2177,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Concentrate strength to deal massive physical damage next turn.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Next Physical Hit: +80% -&gt; +110% -&gt; +140% -&gt; +170% -&gt; +200% (L1-5)
+TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14    |    Applies to next physical action</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Physical charge.</t>
         </is>
       </c>
     </row>
@@ -1916,9 +2236,25 @@
           <t>LvUp: Steal success UP Time until next turn DOWN</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Attempt to pilfer pocket money from an enemy.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Success Rate: 40% -&gt; 70% (+7.5%/Lv)    |    Gold: 1.0x -&gt; 2.5x base amount
+TP Cost: 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Steals gold.</t>
         </is>
       </c>
     </row>
@@ -1959,9 +2295,25 @@
           <t>LvUp: Steal success UP Time until next turn DOWN</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Attempt to steal an item from an enemy.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Success Rate: 25% -&gt; 55% (+7.5%/Lv)    |    Levels: L1-5
+TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Steals item.</t>
         </is>
       </c>
     </row>
@@ -2003,9 +2355,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Dagger skill. Strike for guaranteed critical stab damage.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ATK: 130% -&gt; 145% -&gt; 160% -&gt; 175% -&gt; 190% (L1-5)    |    100% Critical Hit
+TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Guaranteed critical.</t>
         </is>
       </c>
     </row>
@@ -2047,9 +2415,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Dagger skill. Damage scales higher per buff and debuff on the target.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Base ATK: 120% -&gt; 160% (L1-5)    |    +25% damage per active buff/debuff
+TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Bonus per status icon.</t>
         </is>
       </c>
     </row>
@@ -2091,9 +2475,25 @@
 Time until next turn DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Increase own physical evasion rate.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>EVA: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5 Max)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8    |    TP Cost: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Evasion boost.</t>
         </is>
       </c>
     </row>
@@ -2179,9 +2579,25 @@
 Time until next turn DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Concentrate to boost own accuracy and critical hit rate.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Accuracy: +20% -&gt; +35% (+3.75%/Lv)    |    Crit: +10% -&gt; +20% (+2.5%/Lv)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8    |    TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Accuracy buff.</t>
         </is>
       </c>
     </row>
@@ -2223,9 +2639,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Enhance own movement and agility for increased turn speed.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Speed: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5 Max)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8    |    TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Speed buff.</t>
         </is>
       </c>
     </row>
@@ -2311,9 +2743,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Short-range strike to one enemy. May inflict Sleep.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>ATK: 110% -&gt; 125% -&gt; 140% -&gt; 155% -&gt; 170% (L1-5)    |    Sleep: 30% -&gt; 60%
+TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Sleep sting.</t>
         </is>
       </c>
     </row>
@@ -2355,9 +2803,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Short-range strike to one enemy. May inflict Silence.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>ATK: 110% -&gt; 125% -&gt; 140% -&gt; 155% -&gt; 170% (L1-5)    |    Silence: 30% -&gt; 60%
+TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Silence sting.</t>
         </is>
       </c>
     </row>
@@ -2399,9 +2863,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Short-range strike to one enemy. May inflict Stun.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>ATK: 110% -&gt; 125% -&gt; 140% -&gt; 155% -&gt; 170% (L1-5)    |    Stun: 25% -&gt; 50%
+TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Stun sting.</t>
         </is>
       </c>
     </row>
@@ -2443,9 +2923,25 @@
 Time until next turn DOWN Power decrease DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Bow and gun skill. Rapid fire multiple shots with escalating crit rate.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Hits: 2 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 (L1-5)    |    ATK: 65% -&gt; 85% per hit
+TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 25</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Multi-shot bow skill.</t>
         </is>
       </c>
     </row>
@@ -2487,9 +2983,25 @@
 Time until next turn DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Bow and gun skill. Fire a precision shot guaranteed to never miss.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>ATK: 125% -&gt; 140% -&gt; 155% -&gt; 170% -&gt; 185% (L1-5)    |    100% Accuracy
+TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Never misses.</t>
         </is>
       </c>
     </row>
@@ -2531,9 +3043,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Bow skill. Unleash a piercing arrow with boosted critical strike rate.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>ATK: 150% -&gt; 170% -&gt; 190% -&gt; 210% -&gt; 230% (L1-5)    |    Crit Rate: +30%
+TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>High crit arrow.</t>
         </is>
       </c>
     </row>
@@ -2575,9 +3103,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Bow and gun skill. Attack one enemy with a toxic shot. May poison.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>ATK: 110% -&gt; 125% -&gt; 140% -&gt; 155% -&gt; 170% (L1-5)    |    Poison: 30% -&gt; 60%
+TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Poison arrow.</t>
         </is>
       </c>
     </row>
@@ -2619,9 +3163,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Bow skill. Attack one enemy with a chilling shot. May freeze.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>ATK: 115% -&gt; 130% -&gt; 145% -&gt; 160% -&gt; 175% (L1-5)    |    Freeze: 25% -&gt; 50%
+TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Freeze arrow.</t>
         </is>
       </c>
     </row>
@@ -2663,9 +3223,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Bow skill. Attack one enemy with an electric shot. May paralyze.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>ATK: 115% -&gt; 130% -&gt; 145% -&gt; 160% -&gt; 175% (L1-5)    |    Paralysis: 25% -&gt; 50%
+TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Paralysis arrow.</t>
         </is>
       </c>
     </row>
@@ -2751,9 +3327,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Bow skill. Fire an arrow volley striking all enemies on screen.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>ATK: 95% -&gt; 110% -&gt; 125% -&gt; 140% -&gt; 155% (L1-5 Max)
+TP Cost: 16 -&gt; 19 -&gt; 22 -&gt; 25 -&gt; 28</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>All-target bow attack.</t>
         </is>
       </c>
     </row>
@@ -2795,9 +3387,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Bow skill. Shower random enemies with arrows over multiple turns.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Hits: 3-5 arrows per wave    |    ATK: 70% -&gt; 95% per arrow (L1-5)
+Duration: 2 -&gt; 3 turns    |    TP Cost: 20 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Multi-turn barrage.</t>
         </is>
       </c>
     </row>
@@ -2839,9 +3447,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Bow skill. Massive piercing shot that penetrates through to the back row.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>ATK: 175% -&gt; 200% -&gt; 225% -&gt; 250% -&gt; 280% (L1-5 Max)
+TP Cost: 18 -&gt; 22 -&gt; 26 -&gt; 30 -&gt; 34    |    Hits both front and back target</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Row piercing bow shot.</t>
         </is>
       </c>
     </row>
@@ -3447,9 +4071,25 @@
           <t>LvUp: HP recovery UP</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Heal one ally's HP.</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Heal: 12% -&gt; 15% -&gt; 18% -&gt; 21% -&gt; 25% Max HP (L1-5 Max)
+TP Cost: 2 -&gt; 4 -&gt; 6 -&gt; 8 -&gt; 10    |    Affected by Maid Mastery (+10% cap)</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Percent HP healing.</t>
         </is>
       </c>
     </row>
@@ -3490,9 +4130,25 @@
           <t>LvUp: TP recovery UP</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Prepare a snack to restore one ally's TP.</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>TP Heal: 10% -&gt; 11% -&gt; 12% -&gt; 13% -&gt; 15% Max TP (L1-5)
+Action delay: 0.85x    |    TP Cost: 0 (Costs no TP to use)</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Percent TP restore.</t>
         </is>
       </c>
     </row>
@@ -3533,9 +4189,25 @@
           <t>LvUp: TP transfer bonus UP</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Sacrifice all user TP to transfer a magnified amount to an ally.</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>TP Transferred: 100% -&gt; 110% -&gt; 120% -&gt; 130% -&gt; 140% of user's TP (L1-5)
+Leaves user at 0 TP    |    Fast recovery</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>TP battery sacrifice.</t>
         </is>
       </c>
     </row>
@@ -3576,9 +4248,25 @@
           <t>LvUp: Speed increase UP Duration UP</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Clean up battle area to grant party action speed boost.</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Speed: +12% -&gt; +14% -&gt; +16% -&gt; +18% -&gt; +20% (L1-5)
+Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10    |    TP Cost: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Speed buff.</t>
         </is>
       </c>
     </row>
@@ -4097,9 +4785,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>High risk gamble. Unleash 0 to 4 strikes on random enemies.</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>ATK per hit: 90% -&gt; 110% -&gt; 130% -&gt; 150% -&gt; 180% (L1-5)
+TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28    |    Boosted by Trump / High Risk</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>0-4 multi strike.</t>
         </is>
       </c>
     </row>
@@ -4141,9 +4845,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Take a rest to restore own HP and raise Pep. Fast turn recovery.</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Heal: 20% -&gt; 25% -&gt; 30% -&gt; 35% -&gt; 40% Max HP (L1-5 Max)
+TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10    |    Action delay: 1.50x (fast)</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Self heal and pep.</t>
         </is>
       </c>
     </row>
@@ -6889,9 +7609,25 @@
 TP Cost UP Chant time UP</t>
         </is>
       </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Deal fire damage to one enemy.</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Pwr (L1-10): 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520
+TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32  (Lv1 to Max)</t>
+        </is>
+      </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Single target fire.</t>
         </is>
       </c>
     </row>
@@ -7241,9 +7977,25 @@
 TP Cost UP Chant time UP</t>
         </is>
       </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Deal lightning damage to one enemy.</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Pwr (L1-10): 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520
+TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32  (Lv1 to Max)</t>
+        </is>
+      </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Single target lightning.</t>
         </is>
       </c>
     </row>
@@ -7417,9 +8169,25 @@
 TP Cost UP Chant time UP</t>
         </is>
       </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Deal wind damage to one enemy.</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Pwr (L1-10): 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520
+TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32  (Lv1 to Max)</t>
+        </is>
+      </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Single target wind.</t>
         </is>
       </c>
     </row>
@@ -7593,9 +8361,25 @@
 TP Cost UP Chant time UP</t>
         </is>
       </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Deal earth damage to one enemy.</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Pwr (L1-10): 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520
+TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32  (Lv1 to Max)</t>
+        </is>
+      </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Single target earth.</t>
         </is>
       </c>
     </row>
@@ -8825,9 +9609,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Heal an ally's HP.</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Heal Cap (L1-10): 100 -&gt; 150 -&gt; 200 -&gt; 270 -&gt; 350 -&gt; 440 -&gt; 540 -&gt; 650 -&gt; 720 -&gt; 800
+TP Cost: 3 -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26  (Lv1 to Max)</t>
+        </is>
+      </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Single target heal.</t>
         </is>
       </c>
     </row>
@@ -8869,9 +9669,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Heal the entire party's HP.</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Heal Cap (L1-10): 80 -&gt; 120 -&gt; 160 -&gt; 210 -&gt; 270 -&gt; 340 -&gt; 420 -&gt; 510 -&gt; 600 -&gt; 700
+TP Cost: 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 21 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 -&gt; 46  (Lv1 to Max)</t>
+        </is>
+      </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Party heal.</t>
         </is>
       </c>
     </row>
@@ -8912,9 +9728,25 @@
           <t>LvUp: TP Cost DOWN Chant time DOWN</t>
         </is>
       </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Fully restore one ally's HP to maximum.</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Heals 100% Max HP (9,999 HP cap)    |    Chant: 2 turns -&gt; 1 turn
+TP Cost: 35 -&gt; 30 -&gt; 25 -&gt; 20 -&gt; 16 (L1-5)</t>
+        </is>
+      </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Full heal.</t>
         </is>
       </c>
     </row>
@@ -8956,9 +9788,25 @@
 slow &gt; all debuffs TP Cost UP</t>
         </is>
       </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Cure status ailments for a single ally.</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Cures: Poison (L1) -&gt; Paralyze -&gt; Silence -&gt; Freeze -&gt; Sleep -&gt; Petrify -&gt; Slow
+TP Cost: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 (L1-7)</t>
+        </is>
+      </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Single cure.</t>
         </is>
       </c>
     </row>
@@ -9000,9 +9848,25 @@
 slow &gt; all debuffs TP Cost UP</t>
         </is>
       </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Cure status ailments for the entire party.</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Cures: Poison (L1) -&gt; Paralyze -&gt; Silence -&gt; Freeze -&gt; Sleep -&gt; Petrify -&gt; Slow
+TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 (L1-7)</t>
+        </is>
+      </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Party cure.</t>
         </is>
       </c>
     </row>
@@ -9044,9 +9908,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Revive a fallen ally.</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Revival HP: 20% -&gt; 35% -&gt; 50% -&gt; 70% -&gt; 100% Max HP (L1-5)
+Chant time decreases per level    |    TP Cost: 18 -&gt; 22 -&gt; 26 -&gt; 30 -&gt; 35</t>
+        </is>
+      </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Revives ally.</t>
         </is>
       </c>
     </row>
@@ -9088,9 +9968,25 @@
 Time until next turn DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Raise an ally's physical ATK.</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>ATK: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5 Max)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8    |    TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
+        </is>
+      </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Single ATK buff.</t>
         </is>
       </c>
     </row>
@@ -9132,9 +10028,25 @@
 Time until next turn DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Raise an ally's physical DEF.</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>DEF: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5 Max)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8    |    TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
+        </is>
+      </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Single DEF buff.</t>
         </is>
       </c>
     </row>
@@ -9176,9 +10088,25 @@
 Time until next turn DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Raise the party's magical defense against incoming spells.</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>Magic DEF: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8    |    TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
+        </is>
+      </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Magic defense buff.</t>
         </is>
       </c>
     </row>
@@ -9220,9 +10148,25 @@
 Time until next turn DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Raise party resistance to Fire, Water, Lightning, Wind, and Earth.</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>Resist: +15 -&gt; +20 -&gt; +25 -&gt; +30 -&gt; +35 all elements (L1-5)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8    |    TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
+        </is>
+      </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Elemental resistance.</t>
         </is>
       </c>
     </row>
@@ -9264,9 +10208,25 @@
 Chant time DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Raise an ally's action speed.</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Speed: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5)
+Chant time decreases per level    |    TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
+        </is>
+      </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Single speed buff.</t>
         </is>
       </c>
     </row>
@@ -9308,9 +10268,25 @@
 Duration UP Chant time DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Temporarily raise an ally's maximum HP cap.</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Max HP: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8    |    TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22</t>
+        </is>
+      </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Max HP boost.</t>
         </is>
       </c>
     </row>
@@ -9352,9 +10328,25 @@
 slow &gt; all debuffs TP Cost UP</t>
         </is>
       </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Cure status ailments for one row of allies.</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>Cures: Poison (L1) -&gt; Paralyze -&gt; Silence -&gt; Freeze -&gt; Sleep -&gt; Petrify -&gt; Slow
+TP Cost: 7 -&gt; 10 -&gt; 13 -&gt; 16 -&gt; 20 -&gt; 24 -&gt; 28 (L1-7)</t>
+        </is>
+      </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Row cure.</t>
         </is>
       </c>
     </row>
@@ -9396,9 +10388,25 @@
 TP Cost UP Chant time UP</t>
         </is>
       </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Create magical afterimages that let user dodge incoming attacks.</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Dodges: 2 guaranteed physical attacks avoided
+Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5)    |    TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22</t>
+        </is>
+      </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>Afterimage dodge.</t>
         </is>
       </c>
     </row>
@@ -9440,9 +10448,25 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Enchant self with a barrier reducing incoming physical damage.</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>Physical Damage Reduction: -20% -&gt; -35% (-3.75%/Lv)    |    Levels: L1-5
+TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
+        </is>
+      </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>Self physical shield.</t>
         </is>
       </c>
     </row>
@@ -9527,9 +10551,25 @@
           <t>LvUp: Duration UP</t>
         </is>
       </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Illuminate dark dungeons to reveal secret passages and hidden doors.</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>Duration: 50 -&gt; 100 -&gt; 150 -&gt; 200 -&gt; 300 steps (L1-5)
+TP Cost: 4 -&gt; 4 -&gt; 4 -&gt; 4 -&gt; 4</t>
+        </is>
+      </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>Illumination.</t>
         </is>
       </c>
     </row>
@@ -9570,9 +10610,25 @@
           <t>LvUp: TP Cost DOWN</t>
         </is>
       </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Immediately teleport the party safely out of the dungeon.</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>TP Cost: 20 -&gt; 15 -&gt; 10 -&gt; 6 -&gt; 2 (L1-5 Max)
+Works identical to an Emergency Exit item</t>
+        </is>
+      </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>Dungeon escape.</t>
         </is>
       </c>
     </row>
@@ -9613,9 +10669,25 @@
           <t>LvUp: Accuracy UP Chant time DOWN</t>
         </is>
       </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Sing a soothing lullaby. May put target enemy to sleep.</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>Sleep Chance: 40% -&gt; 70% (+7.5%/Lv)    |    Levels: L1-5
+TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
+        </is>
+      </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>Sleep chant.</t>
         </is>
       </c>
     </row>
@@ -9866,9 +10938,25 @@
           <t>LvUp: HP recovery UP Chant time DOWN</t>
         </is>
       </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Perform a song that regenerates party HP every turn while singing.</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>HP Regen: 8% -&gt; 11% -&gt; 14% -&gt; 17% -&gt; 20% Max HP per turn (L1-5)
+Chant Time: 2 turns -&gt; 1 turn    |    TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
+        </is>
+      </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>Song HP regen.</t>
         </is>
       </c>
     </row>
@@ -9909,9 +10997,25 @@
           <t>LvUp: TP recovery UP Chant time DOWN</t>
         </is>
       </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Perform a song that regenerates party TP every turn while singing.</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>TP Regen: 3 -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 12 TP per turn (L1-5)
+Chant Time: 2 turns -&gt; 1 turn    |    TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22</t>
+        </is>
+      </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>Song TP regen.</t>
         </is>
       </c>
     </row>
@@ -9952,9 +11056,25 @@
           <t>LvUp: Speed increase UP Chant time DOWN</t>
         </is>
       </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Perform a lively march boosting party action speed while singing.</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Party Speed: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5)
+TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22</t>
+        </is>
+      </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>Song speed boost.</t>
         </is>
       </c>
     </row>
@@ -9995,9 +11115,25 @@
           <t>LvUp: EXP increase UP Chant time DOWN</t>
         </is>
       </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Perform a song that increases combat EXP gained by the party.</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>EXP Bonus: +10% -&gt; +15% -&gt; +20% -&gt; +25% -&gt; +30% (L1-5)
+TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
+        </is>
+      </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>EXP song.</t>
         </is>
       </c>
     </row>
@@ -10522,9 +11658,25 @@
 Time until next turn DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Raise the entire party's physical ATK.</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>Party ATK: +10% -&gt; +13% -&gt; +16% -&gt; +20% -&gt; +25% (L1-5)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8    |    TP Cost: 14 -&gt; 18 -&gt; 22 -&gt; 26 -&gt; 30</t>
+        </is>
+      </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>Party ATK buff.</t>
         </is>
       </c>
     </row>
@@ -10566,9 +11718,25 @@
 Time until next turn DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Raise the entire party's physical DEF.</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>Party DEF: +10% -&gt; +13% -&gt; +16% -&gt; +20% -&gt; +25% (L1-5)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8    |    TP Cost: 14 -&gt; 18 -&gt; 22 -&gt; 26 -&gt; 30</t>
+        </is>
+      </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>Party DEF buff.</t>
         </is>
       </c>
     </row>
@@ -11138,9 +12306,25 @@
 dummy</t>
         </is>
       </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Occasionally reflects incoming damage back as fixed neutral damage.</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>Reflect Rate: 20% chance to reflect 30% of received damage to attacker
+Heroine: Melvy</t>
+        </is>
+      </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>Melvy unique.</t>
         </is>
       </c>
     </row>
@@ -11188,8 +12372,8 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>ATK: +3% (L1) -&gt; +5% (L2) -&gt; +7% (L3) -&gt; +9% (L4) -&gt; +10% (L5)... +15% (L10 Max).
-Growth: +2%/Lv for Lv1-4, then +1%/Lv for Lv5-10.</t>
+          <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
+Scales off weapon base ATK (not total character ATK)</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -11199,7 +12383,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>Scales off base weapon ATK, not total character ATK.</t>
+          <t>Weapon mastery.</t>
         </is>
       </c>
     </row>
@@ -11247,8 +12431,8 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>ATK: +3% (L1) -&gt; +5% (L2) -&gt; +7% (L3) -&gt; +9% (L4) -&gt; +10% (L5)... +15% (L10 Max).
-Growth: +2%/Lv for Lv1-4, then +1%/Lv for Lv5-10.</t>
+          <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
+Scales off weapon base ATK</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -11258,7 +12442,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>Scales off base weapon ATK.</t>
+          <t>Weapon mastery.</t>
         </is>
       </c>
     </row>
@@ -11299,9 +12483,25 @@
           <t>LvUp: ATK bonus UP</t>
         </is>
       </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Increases equipped dagger base ATK.</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
+Scales off weapon base ATK</t>
+        </is>
+      </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>Weapon mastery.</t>
         </is>
       </c>
     </row>
@@ -11342,9 +12542,25 @@
           <t>LvUp: ATK bonus UP</t>
         </is>
       </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Increases equipped mace base ATK.</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
+Scales off weapon base ATK</t>
+        </is>
+      </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>Weapon mastery.</t>
         </is>
       </c>
     </row>
@@ -11392,8 +12608,8 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>ATK: +3% (L1) -&gt; +5% (L2) -&gt; +7% (L3) -&gt; +9% (L4) -&gt; +10% (L5)... +15% (L10 Max).
-Growth: +2%/Lv for Lv1-4, then +1%/Lv for Lv5-10.</t>
+          <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
+Scales off weapon base ATK</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -11403,7 +12619,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>Scales off base weapon ATK.</t>
+          <t>Weapon mastery.</t>
         </is>
       </c>
     </row>
@@ -11444,9 +12660,25 @@
           <t>LvUp: ATK bonus UP</t>
         </is>
       </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Increases equipped bow base ATK.</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
+Scales off weapon base ATK</t>
+        </is>
+      </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>Weapon mastery.</t>
         </is>
       </c>
     </row>
@@ -11487,9 +12719,25 @@
           <t>LvUp: ATK bonus UP</t>
         </is>
       </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Increases equipped katana base ATK.</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
+Scales off weapon base ATK</t>
+        </is>
+      </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>Weapon mastery.</t>
         </is>
       </c>
     </row>
@@ -11530,9 +12778,25 @@
           <t>LvUp: ATK bonus UP</t>
         </is>
       </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Increases equipped projectile weapon base ATK.</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
+Scales off weapon base ATK</t>
+        </is>
+      </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>Weapon mastery.</t>
         </is>
       </c>
     </row>
@@ -11573,9 +12837,25 @@
           <t>LvUp: ATK bonus UP</t>
         </is>
       </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Increases equipped whip base ATK.</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
+Scales off weapon base ATK</t>
+        </is>
+      </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>Weapon mastery.</t>
         </is>
       </c>
     </row>
@@ -11616,9 +12896,25 @@
           <t>LvUp: ATK bonus UP</t>
         </is>
       </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Increases equipped fan base ATK.</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>ATK (L1-10): +3% -&gt; +5% -&gt; +7% -&gt; +9% -&gt; +10% to +15% (+1%/Lv after L4)
+Scales off weapon base ATK</t>
+        </is>
+      </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>Weapon mastery.</t>
         </is>
       </c>
     </row>
@@ -11659,9 +12955,25 @@
           <t>LvUp: ATK bonus UP</t>
         </is>
       </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Increases equipped base ATK for all weapon types.</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>ATK (L1-10): +2% -&gt; +3% -&gt; +4% -&gt; +5% -&gt; +6% -&gt; +7% -&gt; +8% -&gt; +9% -&gt; +10% -&gt; +12%
+Universal weapon scaling</t>
+        </is>
+      </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>All weapon mastery.</t>
         </is>
       </c>
     </row>
@@ -11702,9 +13014,25 @@
           <t>LvUp: Magic attack bonus UP</t>
         </is>
       </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Increase magic attack power bonus for all spells.</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>Magic Power (L1-10): +6% (L1) -&gt; +15% (L10 Max)    |    Step: +1%/Lv (+6% base)
+Applies to all offensive spell damage</t>
+        </is>
+      </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>Magic power bonus.</t>
         </is>
       </c>
     </row>
@@ -11745,9 +13073,25 @@
           <t>LvUp: HP recovery bonus UP Recovery cap UP</t>
         </is>
       </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Boost potency and maximum HP healing cap of healing magic.</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>Healing Bonus: +10% -&gt; +30% (+2%/Lv up to L5, then +3%/Lv, Max +30%)
+Also raises baseline healing cap on Heal and Circle Heal</t>
+        </is>
+      </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>Healing power bonus.</t>
         </is>
       </c>
     </row>
@@ -11788,9 +13132,25 @@
           <t>LvUp: HP recovery UP</t>
         </is>
       </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Recover HP every turn during battle.</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>HP Regen: 10 -&gt; 20 -&gt; 30 -&gt; 40 -&gt; 50 HP per turn (L1-5)
+Triggers at start of user's action in combat</t>
+        </is>
+      </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>HP regen.</t>
         </is>
       </c>
     </row>
@@ -11874,9 +13234,25 @@
           <t>LvUp: TP recovery UP</t>
         </is>
       </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Recover TP every turn during battle.</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>TP Regen (L1-10): 2 -&gt; 3 -&gt; 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 15 -&gt; 16 TP per turn
+Active on user turn in battle</t>
+        </is>
+      </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>TP regen.</t>
         </is>
       </c>
     </row>
@@ -11917,9 +13293,25 @@
           <t>LvUp: TP recovery UP</t>
         </is>
       </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Slightly recover TP every turn during battle.</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>TP Regen: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 TP per turn (L1-8)
+Triggers on user turn in combat</t>
+        </is>
+      </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>Minor TP regen.</t>
         </is>
       </c>
     </row>
@@ -11960,9 +13352,25 @@
           <t>LvUp: Elemental resistance UP</t>
         </is>
       </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Raise innate resistance to all elements.</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>Elemental Resist: +5 -&gt; +10 -&gt; +15 -&gt; +20 -&gt; +25 all elements (L1-5)
+Applies to Fire, Water, Lightning, Wind, and Earth</t>
+        </is>
+      </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>All element resist.</t>
         </is>
       </c>
     </row>
@@ -12010,8 +13418,8 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Counter: 6% (L1) -&gt; 9% (L2) -&gt; 12% (L3) -&gt; 15% (L4) -&gt; 18% (L5 Max).
-Caution: short-range retaliations will trigger enemy Dark Aura.</t>
+          <t>Counter Rate: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5)    |    Step: +3%/Lv
+Note: Short-range retaliations will trigger enemy Dark Aura</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -12021,7 +13429,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>Counter range matches weapon reach. Beware Dark Aura.</t>
+          <t>Physical counter.</t>
         </is>
       </c>
     </row>
@@ -12062,9 +13470,25 @@
           <t>LvUp: Activation rate UP</t>
         </is>
       </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Occasionally parry and counterattack when targeted by an enemy.</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>Parry &amp; Counter: 10% -&gt; 25% (+3.75%/Lv)    |    Levels: L1-5
+Nullifies incoming attack and strikes back</t>
+        </is>
+      </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>Parry counter.</t>
         </is>
       </c>
     </row>
@@ -12112,8 +13536,8 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>Trigger: 9% (L1) -&gt; 12% (L2) -&gt; 15% (L3) -&gt; 18% (L4) -&gt; 21% (L5 Max).
-Can stack with Triple Attack (up to 5 strikes total).</t>
+          <t>Trigger Rate: 9% -&gt; 12% -&gt; 15% -&gt; 18% -&gt; 21% (L1-5)    |    Step: +3%/Lv
+Can stack with Triple Attack (up to 5 strikes total)</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -12123,7 +13547,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>High synergy with Luco unique skill.</t>
+          <t>Double strike.</t>
         </is>
       </c>
     </row>
@@ -12164,9 +13588,25 @@
           <t>LvUp: Triple attack rate UP</t>
         </is>
       </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Chance to attack thrice when using normal attacks.</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>Trigger Rate: 5% -&gt; 7.5% -&gt; 10% -&gt; 12.5% -&gt; 15% (L1-5)    |    Step: +2.5%/Lv
+Stacks with Double Attack</t>
+        </is>
+      </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>Triple strike.</t>
         </is>
       </c>
     </row>
@@ -12293,9 +13733,25 @@
           <t>LvUp: Survival rate UP</t>
         </is>
       </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Occasionally survive at 1 HP after receiving fatal damage.</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>Survival Rate: 20% -&gt; 30% -&gt; 40% -&gt; 50% -&gt; 60% (L1-5)    |    Step: +10%/Lv
+Prevents death when hit by lethal blows</t>
+        </is>
+      </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>Fatal survival.</t>
         </is>
       </c>
     </row>
@@ -12336,9 +13792,25 @@
           <t>LvUp: Auto-guard rate UP</t>
         </is>
       </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Occasionally Defend automatically when receiving physical attacks.</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>Auto-Guard Rate: 10% -&gt; 15% -&gt; 20% -&gt; 25% -&gt; 30% (L1-5)    |    Step: +5%/Lv
+Halves incoming damage when triggered</t>
+        </is>
+      </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>Auto defense.</t>
         </is>
       </c>
     </row>
@@ -12379,9 +13851,25 @@
           <t>LvUp: Sub-weapon ATK UP</t>
         </is>
       </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Equip two one-handed weapons simultaneously.</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>Off-Hand ATK: 50% -&gt; 57.5% -&gt; 65% -&gt; 72.5% -&gt; 80% (L1-5)    |    Step: +7.5%/Lv
+Main hand weapon deals 100% ATK</t>
+        </is>
+      </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>Dual weapons.</t>
         </is>
       </c>
     </row>
@@ -12971,9 +14459,25 @@
           <t>LvUp: Interruption rate DOWN</t>
         </is>
       </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Make it harder for chants, songs, and dances to be interrupted.</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>Interruption Resist: +20% -&gt; +50% (+7.5%/Lv)    |    Levels: L1-5
+Crucial for casters and performers in front row</t>
+        </is>
+      </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>Chant protection.</t>
         </is>
       </c>
     </row>
@@ -13014,9 +14518,25 @@
           <t>LvUp: Chant time DOWN</t>
         </is>
       </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Reduce chant time required to cast spells.</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>Chant Time Reduction: -10% -&gt; -30% (-5%/Lv)    |    Levels: L1-5
+Accelerates offensive and healing magic activation</t>
+        </is>
+      </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>Chant acceleration.</t>
         </is>
       </c>
     </row>
@@ -13057,9 +14577,25 @@
           <t>LvUp: TP Cost reduction UP</t>
         </is>
       </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Reduce TP consumption in battle.</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>TP Cost Reduction: -10% -&gt; -15% -&gt; -20% -&gt; -25% -&gt; -30% (L1-5)
+Lowers cost of all techniques and spells</t>
+        </is>
+      </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>TP discount.</t>
         </is>
       </c>
     </row>
@@ -13272,9 +14808,25 @@
           <t>LvUp: Item drop rate UP</t>
         </is>
       </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Increase enemies' item drop rate after battle.</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>Item Drop Rate: +10% -&gt; +15% -&gt; +20% -&gt; +25% -&gt; +30% (L1-5)
+Boosts party equipment and material acquisition</t>
+        </is>
+      </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>Drop rate buff.</t>
         </is>
       </c>
     </row>
@@ -13315,9 +14867,25 @@
           <t>LvUp: Gold drop rate UP</t>
         </is>
       </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Increase amount of gold dropped by defeated enemies.</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>Gold Gain: +15% -&gt; +23% -&gt; +32% -&gt; +41% -&gt; +50% (L1-5)
+Earn bonus currency after every battle</t>
+        </is>
+      </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>Gold boost.</t>
         </is>
       </c>
     </row>
@@ -13487,9 +15055,25 @@
           <t>LvUp: Item effects UP</t>
         </is>
       </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>Increase effects of HP and TP recovery items during battle.</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>Item Potency: +20% -&gt; +30% -&gt; +40% -&gt; +50% -&gt; +60% (L1-5)
+Applies to all consumable recovery items used in combat</t>
+        </is>
+      </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>Item potency.</t>
         </is>
       </c>
     </row>
@@ -13702,9 +15286,25 @@
           <t>LvUp: Maid skill bonus UP</t>
         </is>
       </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>Increased potency and effectiveness for all maid skills.</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>Maid Skill Bonus: +2% -&gt; +4% -&gt; +6% -&gt; +8% -&gt; +10% (L1-5)
+Empowers First Aid, Cook, and Clean</t>
+        </is>
+      </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>Maid bonus.</t>
         </is>
       </c>
     </row>
@@ -13745,9 +15345,25 @@
           <t>LvUp: Singing skill bonus UP</t>
         </is>
       </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>Increased potency and effectiveness for all songs.</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>Song Potency: +3% -&gt; +6% -&gt; +9% -&gt; +12% -&gt; +15% (L1-5)
+Empowers Bard songs and regeneration rates</t>
+        </is>
+      </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>Song bonus.</t>
         </is>
       </c>
     </row>
@@ -13788,9 +15404,25 @@
           <t>LvUp: Dancing skill bonus UP</t>
         </is>
       </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>Increased potency and effectiveness for all dances.</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>Dance Potency: +3% -&gt; +6% -&gt; +9% -&gt; +12% -&gt; +15% (L1-5)
+Empowers Dancer dances and status effects</t>
+        </is>
+      </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>Dance bonus.</t>
         </is>
       </c>
     </row>
@@ -14193,9 +15825,25 @@
           <t>Occasionally land critical hits with offensive spells.</t>
         </is>
       </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>Occasionally land critical hits with offensive spells.</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>Spell Crit Rate: +10% -&gt; +13.75% -&gt; +17.5% -&gt; +21.25% -&gt; +25% (L1-5)
+Spell criticals deal 1.50x normal magic damage</t>
+        </is>
+      </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>Spell critical.</t>
         </is>
       </c>
     </row>
@@ -14269,9 +15917,25 @@
           <t>Significantly increase damage according to Pep.</t>
         </is>
       </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>Significantly increase damage according to Pep.</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>Damage: +1% per Pep point (up to +100% damage at Max Pep)
+Heroine: Luco    |    Scales with high morale</t>
+        </is>
+      </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>Luco unique.</t>
         </is>
       </c>
     </row>
@@ -14307,9 +15971,25 @@
           <t>Occasionally inflict enemies with status ailments or Dispel at random.</t>
         </is>
       </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>Occasionally inflict enemies with status ailments or Dispel at random.</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>Activation Rate: 15% on enemy action    |    Heroine: Mefmera
+Inflicts Poison, Paralyze, Silence, or cancels enemy buffs</t>
+        </is>
+      </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>Mefmera unique.</t>
         </is>
       </c>
     </row>
@@ -14345,9 +16025,25 @@
           <t>May counter short-range attacks with Slow and a Speed decrease.</t>
         </is>
       </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>Counter short-range physical attacks with Slow and Speed decrease.</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>Counter Rate: 25% on physical contact    |    Inflicts -30% Speed
+Heroine: Souffle</t>
+        </is>
+      </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>Souffle unique.</t>
         </is>
       </c>
     </row>
@@ -14383,9 +16079,25 @@
           <t>Increase weapon modifier when attacking with weapon-based skills.</t>
         </is>
       </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Increase weapon modifier when attacking with weapon-based skills.</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>Weapon Scaling: +25% damage to all weapon-based techniques
+Heroine: Grishna</t>
+        </is>
+      </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>Grishna unique.</t>
         </is>
       </c>
     </row>
@@ -14421,9 +16133,25 @@
           <t>May guarantee a hit and bypass DEF with physical attacks or skills.</t>
         </is>
       </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>May guarantee a 100% hit and bypass enemy DEF with physical attacks.</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>Activation Rate: 20% on physical strikes    |    Ignores target DEF
+Heroine: Yae</t>
+        </is>
+      </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>Yae unique.</t>
         </is>
       </c>
     </row>
@@ -14459,9 +16187,25 @@
           <t>Occasionally nullify all damage received from enemies.</t>
         </is>
       </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Occasionally nullify all damage received from enemies.</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>Nullification Rate: 10% chance to completely negate incoming damage
+Heroine: Lize</t>
+        </is>
+      </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>Lize unique.</t>
         </is>
       </c>
     </row>
@@ -14497,9 +16241,25 @@
           <t>Before acting, may erase enemy puppets, familiars, shikigami, or slaves.</t>
         </is>
       </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Before acting, may erase enemy puppets, familiars, or summons.</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>Banish Rate: 25% chance to instantly eliminate enemy summon entities
+Heroine: Lilian</t>
+        </is>
+      </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>Lilian unique.</t>
         </is>
       </c>
     </row>
@@ -14535,9 +16295,25 @@
           <t>Before acting, may use an item from her own personal stock.</t>
         </is>
       </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Before acting, may use an item from personal stock without cost.</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>Trigger Rate: 20% chance to use free recovery item at turn start
+Heroine: Monica</t>
+        </is>
+      </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>Monica unique.</t>
         </is>
       </c>
     </row>
@@ -14573,9 +16349,25 @@
           <t>Decrease turn delay after using skills or magic.</t>
         </is>
       </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>Decrease turn delay after using skills or magic.</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>Action Delay Reduction: -20% recovery delay after any action
+Heroine: Alisia</t>
+        </is>
+      </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>Alisia unique.</t>
         </is>
       </c>
     </row>
@@ -14611,9 +16403,25 @@
           <t>Increased effects for all maid skills.</t>
         </is>
       </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>Increased potency and effectiveness for all maid skills.</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>Maid Skill Potency: +15% effectiveness to First Aid, Cook, etc.
+Heroine: Conette</t>
+        </is>
+      </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>Conette unique.</t>
         </is>
       </c>
     </row>
@@ -14649,9 +16457,25 @@
           <t>May occasionally act twice in one turn.</t>
         </is>
       </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>May occasionally act twice in one turn.</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>Double Action Rate: 15% chance to receive an extra turn immediately
+Heroine: Yuni</t>
+        </is>
+      </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>Yuni unique.</t>
         </is>
       </c>
     </row>
@@ -14687,9 +16511,25 @@
           <t>If killed, revive after a certain number of turns.</t>
         </is>
       </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>If killed in battle, revive after 3 turns.</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>Auto-Revive: Resurrects with 50% HP after 3 combat turns
+Heroine: Gina</t>
+        </is>
+      </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>Gina unique.</t>
         </is>
       </c>
     </row>
@@ -14725,9 +16565,25 @@
           <t>Whole row takes less damage from Demons, Undead, and Apparitions.</t>
         </is>
       </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>Whole row takes less damage from Demons, Undead, and Apparitions.</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>Row Damage Mitigation: -20% incoming damage from specified monster types
+Heroine: Ist</t>
+        </is>
+      </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>Ist unique.</t>
         </is>
       </c>
     </row>
@@ -14763,9 +16619,25 @@
           <t>May lower all enemies' ATK and INT with heart-penetrating vocals.</t>
         </is>
       </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>May lower all enemies' ATK and INT at start of turn.</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>Trigger Rate: 15% at turn start    |    Inflicts -20% ATK and -20% INT
+Heroine: Fiora</t>
+        </is>
+      </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>Fiora unique.</t>
         </is>
       </c>
     </row>
@@ -14801,9 +16673,25 @@
           <t>Magic will occasionally activate immediately without the need to chant.</t>
         </is>
       </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>Magic will occasionally activate immediately without chanting.</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>Instant Cast Rate: 15% chance for cast spells to trigger with 0 chant time
+Heroine: Eltricia</t>
+        </is>
+      </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>Eltricia unique.</t>
         </is>
       </c>
     </row>
@@ -14839,9 +16727,25 @@
           <t>Occasionally reflects a percentage of damage taken as fixed damage.</t>
         </is>
       </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>Occasionally reflects incoming damage back as fixed neutral damage.</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>Reflect Rate: 20% chance to reflect 30% of received damage to attacker
+Heroine: Melvy</t>
+        </is>
+      </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>Melvy unique.</t>
         </is>
       </c>
     </row>
@@ -14877,9 +16781,25 @@
           <t>Summons another self from the shadows to attack.</t>
         </is>
       </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>Summons a shadow clone on normal attacks to deliver an extra strike.</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>Shadow Strike: Normal attacks trigger an extra hit dealing 75% damage
+Heroine: Tsurara</t>
+        </is>
+      </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>Tsurara unique.</t>
         </is>
       </c>
     </row>
@@ -14915,9 +16835,25 @@
           <t>Increased effects for all class modifiers.</t>
         </is>
       </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>Increased effects for all class modifiers and masteries.</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>Class Stat Potency: +10% to all class stat bonuses and weapon masteries
+Heroine: Siena</t>
+        </is>
+      </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>Siena unique.</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/skills.xlsx
+++ b/mod_project/data_tables/skills.xlsx
@@ -547,12 +547,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Attract single-target attacks.    |    Fast turn recovery.</t>
+          <t>Attract single-target attacks. | Fast turn recovery.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5)    |    Speed: +50% -&gt; +100% (+12.5%/Lv)
+          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5) | Speed: +50% -&gt; +100% (+12.5%/Lv)
 TP Cost: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5</t>
         </is>
       </c>
@@ -612,7 +612,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5)    |    Speed: +40% -&gt; +80% (+10%/Lv)
+          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5) | Speed: +40% -&gt; +80% (+10%/Lv)
 TP Cost: 3 -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 11</t>
         </is>
       </c>
@@ -673,7 +673,7 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>ATK: +8% -&gt; +10% -&gt; +12% -&gt; +14% -&gt; +18% (L1-5 Max)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8    |    TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13</t>
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Short-range strike.    |    Hit Rate: +20% -&gt; +38% (+2%/Lv)</t>
+          <t>Short-range strike. | Hit Rate: +20% -&gt; +38% (+2%/Lv)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Dispel Chance: 30% -&gt; 60% (+7.5%/Lv)    |    Levels: L1-5
+          <t>Dispel Chance: 30% -&gt; 60% (+7.5%/Lv) | Levels: L1-5
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
@@ -852,8 +852,8 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ATK: +25% -&gt; +35% -&gt; +45% -&gt; +55% -&gt; +65% (L1-5)    |    DEF: -15% -&gt; -35%
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8    |    TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
+          <t>ATK: +25% -&gt; +65% (+10%/Lv) | DEF: -15% -&gt; -35% (-5%/Lv)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -913,7 +913,7 @@
       <c r="J8" t="inlineStr">
         <is>
           <t>DEF: +20% -&gt; +27% -&gt; +35% -&gt; +42% -&gt; +50% (L1-5 Max)
-ATK: -11% -&gt; -25% (-3.5%/Lv)    |    TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
+ATK: -11% -&gt; -25% (-3.5%/Lv) | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -972,8 +972,8 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>ATK: 110% -&gt; 120% -&gt; 130% -&gt; 140% -&gt; 150% (L1-5)    |    Stun: 20% -&gt; 40%
-TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14    |    Requires equipped shield</t>
+          <t>ATK: 110% -&gt; 150% (+10%/Lv) | Stun: 20% -&gt; 40% (+5%/Lv)
+TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 | Requires equipped shield</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>ATK: 115% -&gt; 130% -&gt; 145% -&gt; 160% -&gt; 175% (L1-5)    |    Instakill: 10% -&gt; 25%
+          <t>ATK: 115% -&gt; 175% (+15%/Lv) | Instakill: 10% -&gt; 25% (+3.75%/Lv)
 TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 28</t>
         </is>
       </c>
@@ -1180,8 +1180,8 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>ATK: 120% -&gt; 135% -&gt; 150% -&gt; 165% -&gt; 180% (L1-5)    |    DEF Debuff: -15% -&gt; -30%
-TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20    |    Bypasses enemy armor</t>
+          <t>ATK: 120% -&gt; 180% (+15%/Lv) | DEF Debuff: -15% -&gt; -30% (-3.75%/Lv)
+TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 | Bypasses enemy armor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1301,7 +1301,7 @@
       <c r="J15" t="inlineStr">
         <is>
           <t>ATK: 70% -&gt; 80% -&gt; 90% -&gt; 100% -&gt; 110% per hit (3 hits total)
-TP Cost: 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30    |    Target must be living (not undead)</t>
+TP Cost: 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 | Target must be living (not undead)</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1361,7 +1361,7 @@
       <c r="J16" t="inlineStr">
         <is>
           <t>ATK: 110% -&gt; 125% -&gt; 140% -&gt; 155% -&gt; 170% (L1-5)
-HP Absorb: 20% -&gt; 30% -&gt; 40% -&gt; 50% -&gt; 60%    |    TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
+HP Absorb: 20% -&gt; 30% -&gt; 40% -&gt; 50% -&gt; 60% | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1421,7 +1421,7 @@
       <c r="J17" t="inlineStr">
         <is>
           <t>ATK: 100% -&gt; 110% -&gt; 120% -&gt; 130% -&gt; 140% (L1-5)
-TP Absorb: 5% -&gt; 8% -&gt; 11% -&gt; 14% -&gt; 18%    |    TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8</t>
+TP Absorb: 5% -&gt; 8% -&gt; 11% -&gt; 14% -&gt; 18% | TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>ATK: 120% -&gt; 135% -&gt; 150% -&gt; 165% -&gt; 180% (L1-5)    |    Freeze: 20% -&gt; 40%
+          <t>ATK: 120% -&gt; 180% (+15%/Lv) | Freeze: 20% -&gt; 40% (+5%/Lv)
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
         </is>
       </c>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>ATK: 130% -&gt; 150% -&gt; 170% -&gt; 190% -&gt; 210% (L1-5)    |    Petrify: 15% -&gt; 30%
+          <t>ATK: 130% -&gt; 210% (+20%/Lv) | Petrify: 15% -&gt; 30% (+3.75%/Lv)
 TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
         </is>
       </c>
@@ -1601,7 +1601,7 @@
       <c r="J20" t="inlineStr">
         <is>
           <t>ATK: 140% -&gt; 160% -&gt; 180% -&gt; 200% -&gt; 220% (L1-5)
-TP Cost: 16 -&gt; 19 -&gt; 22 -&gt; 25 -&gt; 28    |    Hits 2 sequential turn targets</t>
+TP Cost: 16 -&gt; 19 -&gt; 22 -&gt; 25 -&gt; 28 | Hits 2 sequential turn targets</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1660,8 +1660,8 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5)    |    Guard: 30% -&gt; 60% (+7.5%/Lv)
-TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 20 -&gt; 24    |    Requires 1H weapon &amp; shield</t>
+          <t>Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5) | Guard: 30% -&gt; 60% (+7.5%/Lv)
+TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 20 -&gt; 24 | Requires 1H weapon &amp; shield</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1720,8 +1720,8 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5)    |    Recovery Speed: 1.30x
-TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22    |    May break on repeat blocks</t>
+          <t>Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5) | Recovery Speed: 1.30x
+TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22 | May break on repeat blocks</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>ATK: 140% -&gt; 155% -&gt; 170% -&gt; 185% -&gt; 200% (L1-5)    |    Unholy Bonus: 1.50x
+          <t>ATK: 140% -&gt; 155% -&gt; 170% -&gt; 185% -&gt; 200% (L1-5) | Unholy Bonus: 1.50x
 TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20</t>
         </is>
       </c>
@@ -1840,8 +1840,8 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Damage Reduction: -30% -&gt; -50% (-5%/Lv)    |    Levels: L1-5
-TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26    |    Requires shield</t>
+          <t>Damage Reduction: -30% -&gt; -50% (-5%/Lv) | Levels: L1-5
+TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 | Requires shield</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,8 +1900,8 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Magic Reduction: -30% -&gt; -50% (-5%/Lv)    |    Levels: L1-5
-TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26    |    Requires shield</t>
+          <t>Magic Reduction: -30% -&gt; -50% (-5%/Lv) | Levels: L1-5
+TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 | Requires shield</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>ATK: 110% -&gt; 125% -&gt; 140% -&gt; 155% -&gt; 170% (L1-5)    |    Paralysis: 20% -&gt; 40%
+          <t>ATK: 110% -&gt; 170% (+15%/Lv) | Paralysis: 20% -&gt; 40% (+5%/Lv)
 TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
         </is>
       </c>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>ATK: 125% -&gt; 140% -&gt; 155% -&gt; 170% -&gt; 185% (L1-5)    |    Silence: 20% -&gt; 40%
+          <t>ATK: 125% -&gt; 185% (+15%/Lv) | Silence: 20% -&gt; 40% (+5%/Lv)
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
         </is>
       </c>
@@ -2081,7 +2081,7 @@
       <c r="J28" t="inlineStr">
         <is>
           <t>ATK: 65% -&gt; 75% -&gt; 85% -&gt; 95% -&gt; 105% per hit (L1-5)
-TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 28    |    Heavy Lance bonus: +20% dmg</t>
+TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 28 | Heavy Lance bonus: +20% dmg</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2185,7 +2185,7 @@
       <c r="J30" t="inlineStr">
         <is>
           <t>Next Physical Hit: +80% -&gt; +110% -&gt; +140% -&gt; +170% -&gt; +200% (L1-5)
-TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14    |    Applies to next physical action</t>
+TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 | Applies to next physical action</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Success Rate: 40% -&gt; 70% (+7.5%/Lv)    |    Gold: 1.0x -&gt; 2.5x base amount
+          <t>Success Rate: 40% -&gt; 70% (+7.5%/Lv) | Gold: 1.0x -&gt; 2.5x (+0.375x/Lv)
 TP Cost: 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6</t>
         </is>
       </c>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Success Rate: 25% -&gt; 55% (+7.5%/Lv)    |    Levels: L1-5
+          <t>Success Rate: 25% -&gt; 55% (+7.5%/Lv) | Levels: L1-5
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>ATK: 130% -&gt; 145% -&gt; 160% -&gt; 175% -&gt; 190% (L1-5)    |    100% Critical Hit
+          <t>ATK: 130% -&gt; 145% -&gt; 160% -&gt; 175% -&gt; 190% (L1-5) | 100% Critical Hit
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Base ATK: 120% -&gt; 160% (L1-5)    |    +25% damage per active buff/debuff
+          <t>Base ATK: 120% -&gt; 160% (+10%/Lv) | +25% dmg per active buff/debuff
 TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
         </is>
       </c>
@@ -2483,7 +2483,7 @@
       <c r="J35" t="inlineStr">
         <is>
           <t>EVA: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5 Max)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8    |    TP Cost: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12</t>
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2586,8 +2586,8 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Accuracy: +20% -&gt; +35% (+3.75%/Lv)    |    Crit: +10% -&gt; +20% (+2.5%/Lv)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8    |    TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13</t>
+          <t>Accuracy: +20% -&gt; +35% (+3.75%/Lv) | Crit: +10% -&gt; +20% (+2.5%/Lv)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2647,7 +2647,7 @@
       <c r="J38" t="inlineStr">
         <is>
           <t>Speed: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5 Max)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8    |    TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>ATK: 110% -&gt; 125% -&gt; 140% -&gt; 155% -&gt; 170% (L1-5)    |    Sleep: 30% -&gt; 60%
+          <t>ATK: 110% -&gt; 170% (+15%/Lv) | Sleep: 30% -&gt; 60% (+7.5%/Lv)
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>ATK: 110% -&gt; 125% -&gt; 140% -&gt; 155% -&gt; 170% (L1-5)    |    Silence: 30% -&gt; 60%
+          <t>ATK: 110% -&gt; 170% (+15%/Lv) | Silence: 30% -&gt; 60% (+7.5%/Lv)
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>ATK: 110% -&gt; 125% -&gt; 140% -&gt; 155% -&gt; 170% (L1-5)    |    Stun: 25% -&gt; 50%
+          <t>ATK: 110% -&gt; 170% (+15%/Lv) | Stun: 25% -&gt; 50% (+6.25%/Lv)
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Hits: 2 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 (L1-5)    |    ATK: 65% -&gt; 85% per hit
+          <t>Hits: 2 -&gt; 3 -&gt; 3 -&gt; 4 -&gt; 4 | ATK: 65% -&gt; 85% per hit (+5%/Lv)
 TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 25</t>
         </is>
       </c>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>ATK: 125% -&gt; 140% -&gt; 155% -&gt; 170% -&gt; 185% (L1-5)    |    100% Accuracy
+          <t>ATK: 125% -&gt; 140% -&gt; 155% -&gt; 170% -&gt; 185% (L1-5) | 100% Accuracy
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>ATK: 150% -&gt; 170% -&gt; 190% -&gt; 210% -&gt; 230% (L1-5)    |    Crit Rate: +30%
+          <t>ATK: 150% -&gt; 170% -&gt; 190% -&gt; 210% -&gt; 230% (L1-5) | Crit Rate: +30%
 TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
         </is>
       </c>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>ATK: 110% -&gt; 125% -&gt; 140% -&gt; 155% -&gt; 170% (L1-5)    |    Poison: 30% -&gt; 60%
+          <t>ATK: 110% -&gt; 170% (+15%/Lv) | Poison: 30% -&gt; 60% (+7.5%/Lv)
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>ATK: 115% -&gt; 130% -&gt; 145% -&gt; 160% -&gt; 175% (L1-5)    |    Freeze: 25% -&gt; 50%
+          <t>ATK: 115% -&gt; 175% (+15%/Lv) | Freeze: 25% -&gt; 50% (+6.25%/Lv)
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>ATK: 115% -&gt; 130% -&gt; 145% -&gt; 160% -&gt; 175% (L1-5)    |    Paralysis: 25% -&gt; 50%
+          <t>ATK: 115% -&gt; 175% (+15%/Lv) | Paralysis: 25% -&gt; 50% (+6.25%/Lv)
 TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
@@ -3394,8 +3394,8 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Hits: 3-5 arrows per wave    |    ATK: 70% -&gt; 95% per arrow (L1-5)
-Duration: 2 -&gt; 3 turns    |    TP Cost: 20 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36</t>
+          <t>Hits: 3-5 arrows per wave | ATK: 70% -&gt; 95% per arrow (+6.25%/Lv)
+Duration: 2 -&gt; 3 turns | TP Cost: 20 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3455,7 +3455,7 @@
       <c r="J52" t="inlineStr">
         <is>
           <t>ATK: 175% -&gt; 200% -&gt; 225% -&gt; 250% -&gt; 280% (L1-5 Max)
-TP Cost: 18 -&gt; 22 -&gt; 26 -&gt; 30 -&gt; 34    |    Hits both front and back target</t>
+TP Cost: 18 -&gt; 22 -&gt; 26 -&gt; 30 -&gt; 34 | Hits both front and back target</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4079,7 +4079,7 @@
       <c r="J66" t="inlineStr">
         <is>
           <t>Heal: 12% -&gt; 15% -&gt; 18% -&gt; 21% -&gt; 25% Max HP (L1-5 Max)
-TP Cost: 2 -&gt; 4 -&gt; 6 -&gt; 8 -&gt; 10    |    Affected by Maid Mastery (+10% cap)</t>
+TP Cost: 2 -&gt; 4 -&gt; 6 -&gt; 8 -&gt; 10 | Affected by Maid Mastery (+10% cap)</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4138,7 +4138,7 @@
       <c r="J67" t="inlineStr">
         <is>
           <t>TP Heal: 10% -&gt; 11% -&gt; 12% -&gt; 13% -&gt; 15% Max TP (L1-5)
-Action delay: 0.85x    |    TP Cost: 0 (Costs no TP to use)</t>
+Action delay: 0.85x | TP Cost: 0 (Costs no TP to use)</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4197,7 +4197,7 @@
       <c r="J68" t="inlineStr">
         <is>
           <t>TP Transferred: 100% -&gt; 110% -&gt; 120% -&gt; 130% -&gt; 140% of user's TP (L1-5)
-Leaves user at 0 TP    |    Fast recovery</t>
+Leaves user at 0 TP | Fast recovery</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4256,7 +4256,7 @@
       <c r="J69" t="inlineStr">
         <is>
           <t>Speed: +12% -&gt; +14% -&gt; +16% -&gt; +18% -&gt; +20% (L1-5)
-Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10    |    TP Cost: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12</t>
+Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | TP Cost: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4793,7 +4793,7 @@
       <c r="J81" t="inlineStr">
         <is>
           <t>ATK per hit: 90% -&gt; 110% -&gt; 130% -&gt; 150% -&gt; 180% (L1-5)
-TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28    |    Boosted by Trump / High Risk</t>
+TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 | Boosted by Trump / High Risk</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4853,7 +4853,7 @@
       <c r="J82" t="inlineStr">
         <is>
           <t>Heal: 20% -&gt; 25% -&gt; 30% -&gt; 35% -&gt; 40% Max HP (L1-5 Max)
-TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10    |    Action delay: 1.50x (fast)</t>
+TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 | Action delay: 1.50x (fast)</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Heals 100% Max HP (9,999 HP cap)    |    Chant: 2 turns -&gt; 1 turn
+          <t>Heals 100% Max HP (9,999 HP cap) | Chant: 2 turns -&gt; 1 turn
 TP Cost: 35 -&gt; 30 -&gt; 25 -&gt; 20 -&gt; 16 (L1-5)</t>
         </is>
       </c>
@@ -9916,7 +9916,7 @@
       <c r="J194" t="inlineStr">
         <is>
           <t>Revival HP: 20% -&gt; 35% -&gt; 50% -&gt; 70% -&gt; 100% Max HP (L1-5)
-Chant time decreases per level    |    TP Cost: 18 -&gt; 22 -&gt; 26 -&gt; 30 -&gt; 35</t>
+Chant time decreases per level | TP Cost: 18 -&gt; 22 -&gt; 26 -&gt; 30 -&gt; 35</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -9976,7 +9976,7 @@
       <c r="J195" t="inlineStr">
         <is>
           <t>ATK: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5 Max)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8    |    TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -10036,7 +10036,7 @@
       <c r="J196" t="inlineStr">
         <is>
           <t>DEF: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5 Max)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8    |    TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -10096,7 +10096,7 @@
       <c r="J197" t="inlineStr">
         <is>
           <t>Magic DEF: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8    |    TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -10156,7 +10156,7 @@
       <c r="J198" t="inlineStr">
         <is>
           <t>Resist: +15 -&gt; +20 -&gt; +25 -&gt; +30 -&gt; +35 all elements (L1-5)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8    |    TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -10216,7 +10216,7 @@
       <c r="J199" t="inlineStr">
         <is>
           <t>Speed: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5)
-Chant time decreases per level    |    TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
+Chant time decreases per level | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -10276,7 +10276,7 @@
       <c r="J200" t="inlineStr">
         <is>
           <t>Max HP: +15% -&gt; +20% -&gt; +25% -&gt; +30% -&gt; +35% (L1-5)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8    |    TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22</t>
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -10396,7 +10396,7 @@
       <c r="J202" t="inlineStr">
         <is>
           <t>Dodges: 2 guaranteed physical attacks avoided
-Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5)    |    TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22</t>
+Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5) | TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>Physical Damage Reduction: -20% -&gt; -35% (-3.75%/Lv)    |    Levels: L1-5
+          <t>Physical Damage Reduction: -20% -&gt; -35% (-3.75%/Lv) | Levels: L1-5
 TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
         </is>
       </c>
@@ -10676,7 +10676,7 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>Sleep Chance: 40% -&gt; 70% (+7.5%/Lv)    |    Levels: L1-5
+          <t>Sleep Chance: 40% -&gt; 70% (+7.5%/Lv) | Levels: L1-5
 TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
         </is>
       </c>
@@ -10946,7 +10946,7 @@
       <c r="J213" t="inlineStr">
         <is>
           <t>HP Regen: 8% -&gt; 11% -&gt; 14% -&gt; 17% -&gt; 20% Max HP per turn (L1-5)
-Chant Time: 2 turns -&gt; 1 turn    |    TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
+Chant Time: 2 turns -&gt; 1 turn | TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -11005,7 +11005,7 @@
       <c r="J214" t="inlineStr">
         <is>
           <t>TP Regen: 3 -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 12 TP per turn (L1-5)
-Chant Time: 2 turns -&gt; 1 turn    |    TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22</t>
+Chant Time: 2 turns -&gt; 1 turn | TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -11666,7 +11666,7 @@
       <c r="J228" t="inlineStr">
         <is>
           <t>Party ATK: +10% -&gt; +13% -&gt; +16% -&gt; +20% -&gt; +25% (L1-5)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8    |    TP Cost: 14 -&gt; 18 -&gt; 22 -&gt; 26 -&gt; 30</t>
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 14 -&gt; 18 -&gt; 22 -&gt; 26 -&gt; 30</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -11726,7 +11726,7 @@
       <c r="J229" t="inlineStr">
         <is>
           <t>Party DEF: +10% -&gt; +13% -&gt; +16% -&gt; +20% -&gt; +25% (L1-5)
-Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8    |    TP Cost: 14 -&gt; 18 -&gt; 22 -&gt; 26 -&gt; 30</t>
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 14 -&gt; 18 -&gt; 22 -&gt; 26 -&gt; 30</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Magic Power (L1-10): +6% (L1) -&gt; +15% (L10 Max)    |    Step: +1%/Lv (+6% base)
+          <t>Magic Power (L1-10): +6% (L1) -&gt; +15% (L10 Max) | Step: +1%/Lv (+6% base)
 Applies to all offensive spell damage</t>
         </is>
       </c>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Counter Rate: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5)    |    Step: +3%/Lv
+          <t>Counter Rate: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5) | Step: +3%/Lv
 Note: Short-range retaliations will trigger enemy Dark Aura</t>
         </is>
       </c>
@@ -13477,7 +13477,7 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Parry &amp; Counter: 10% -&gt; 25% (+3.75%/Lv)    |    Levels: L1-5
+          <t>Parry &amp; Counter: 10% -&gt; 25% (+3.75%/Lv) | Levels: L1-5
 Nullifies incoming attack and strikes back</t>
         </is>
       </c>
@@ -13536,7 +13536,7 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>Trigger Rate: 9% -&gt; 12% -&gt; 15% -&gt; 18% -&gt; 21% (L1-5)    |    Step: +3%/Lv
+          <t>Trigger Rate: 9% -&gt; 12% -&gt; 15% -&gt; 18% -&gt; 21% (L1-5) | Step: +3%/Lv
 Can stack with Triple Attack (up to 5 strikes total)</t>
         </is>
       </c>
@@ -13595,7 +13595,7 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>Trigger Rate: 5% -&gt; 7.5% -&gt; 10% -&gt; 12.5% -&gt; 15% (L1-5)    |    Step: +2.5%/Lv
+          <t>Trigger Rate: 5% -&gt; 7.5% -&gt; 10% -&gt; 12.5% -&gt; 15% (L1-5) | Step: +2.5%/Lv
 Stacks with Double Attack</t>
         </is>
       </c>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>Survival Rate: 20% -&gt; 30% -&gt; 40% -&gt; 50% -&gt; 60% (L1-5)    |    Step: +10%/Lv
+          <t>Survival Rate: 20% -&gt; 30% -&gt; 40% -&gt; 50% -&gt; 60% (L1-5) | Step: +10%/Lv
 Prevents death when hit by lethal blows</t>
         </is>
       </c>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Auto-Guard Rate: 10% -&gt; 15% -&gt; 20% -&gt; 25% -&gt; 30% (L1-5)    |    Step: +5%/Lv
+          <t>Auto-Guard Rate: 10% -&gt; 15% -&gt; 20% -&gt; 25% -&gt; 30% (L1-5) | Step: +5%/Lv
 Halves incoming damage when triggered</t>
         </is>
       </c>
@@ -13858,7 +13858,7 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>Off-Hand ATK: 50% -&gt; 57.5% -&gt; 65% -&gt; 72.5% -&gt; 80% (L1-5)    |    Step: +7.5%/Lv
+          <t>Off-Hand ATK: 50% -&gt; 57.5% -&gt; 65% -&gt; 72.5% -&gt; 80% (L1-5) | Step: +7.5%/Lv
 Main hand weapon deals 100% ATK</t>
         </is>
       </c>
@@ -14466,7 +14466,7 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>Interruption Resist: +20% -&gt; +50% (+7.5%/Lv)    |    Levels: L1-5
+          <t>Interruption Resist: +20% -&gt; +50% (+7.5%/Lv) | Levels: L1-5
 Crucial for casters and performers in front row</t>
         </is>
       </c>
@@ -14525,7 +14525,7 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>Chant Time Reduction: -10% -&gt; -30% (-5%/Lv)    |    Levels: L1-5
+          <t>Chant Time Reduction: -10% -&gt; -30% (-5%/Lv) | Levels: L1-5
 Accelerates offensive and healing magic activation</t>
         </is>
       </c>
@@ -15919,15 +15919,11 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>Significantly increase damage according to Pep.</t>
-        </is>
-      </c>
-      <c r="J314" t="inlineStr">
-        <is>
-          <t>Damage: +1% per Pep point (up to +100% damage at Max Pep)
-Heroine: Luco    |    Scales with high morale</t>
-        </is>
-      </c>
+          <t>Heroine: Luco | Damage scales with Pep.
+Effect: +1% damage per Pep point (up to +100% damage at Max Pep).</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr"/>
       <c r="K314" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -15973,15 +15969,11 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>Occasionally inflict enemies with status ailments or Dispel at random.</t>
-        </is>
-      </c>
-      <c r="J315" t="inlineStr">
-        <is>
-          <t>Activation Rate: 15% on enemy action    |    Heroine: Mefmera
-Inflicts Poison, Paralyze, Silence, or cancels enemy buffs</t>
-        </is>
-      </c>
+          <t>Heroine: Mefmera | 15% trigger chance on enemy action.
+Inflicts Poison, Paralyze, Silence, or cancels enemy buffs.</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr"/>
       <c r="K315" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16027,15 +16019,11 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>Counter short-range physical attacks with Slow and Speed decrease.</t>
-        </is>
-      </c>
-      <c r="J316" t="inlineStr">
-        <is>
-          <t>Counter Rate: 25% on physical contact    |    Inflicts -30% Speed
-Heroine: Souffle</t>
-        </is>
-      </c>
+          <t>Heroine: Souffle | 25% counter chance on physical contact.
+Inflicts Slow and -30% Speed on attacker.</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr"/>
       <c r="K316" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16081,15 +16069,11 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>Increase weapon modifier when attacking with weapon-based skills.</t>
-        </is>
-      </c>
-      <c r="J317" t="inlineStr">
-        <is>
-          <t>Weapon Scaling: +25% damage to all weapon-based techniques
-Heroine: Grishna</t>
-        </is>
-      </c>
+          <t>Heroine: Grishna | Weapon Scaling Bonus.
+Grants +25% extra damage to all weapon-based techniques.</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr"/>
       <c r="K317" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16135,15 +16119,11 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>May guarantee a 100% hit and bypass enemy DEF with physical attacks.</t>
-        </is>
-      </c>
-      <c r="J318" t="inlineStr">
-        <is>
-          <t>Activation Rate: 20% on physical strikes    |    Ignores target DEF
-Heroine: Yae</t>
-        </is>
-      </c>
+          <t>Heroine: Yae | 20% activation rate on physical attacks.
+Guarantees 100% hit rate and completely ignores target DEF.</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr"/>
       <c r="K318" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16189,15 +16169,11 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>Occasionally nullify all damage received from enemies.</t>
-        </is>
-      </c>
-      <c r="J319" t="inlineStr">
-        <is>
-          <t>Nullification Rate: 10% chance to completely negate incoming damage
-Heroine: Lize</t>
-        </is>
-      </c>
+          <t>Heroine: Lize | 10% nullification rate.
+Chance to completely negate all incoming damage.</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr"/>
       <c r="K319" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16243,15 +16219,11 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>Before acting, may erase enemy puppets, familiars, or summons.</t>
-        </is>
-      </c>
-      <c r="J320" t="inlineStr">
-        <is>
-          <t>Banish Rate: 25% chance to instantly eliminate enemy summon entities
-Heroine: Lilian</t>
-        </is>
-      </c>
+          <t>Heroine: Lilian | 25% banish rate before acting.
+Instantly eliminates enemy summon entities, puppets, and familiars.</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr"/>
       <c r="K320" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16297,15 +16269,11 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>Before acting, may use an item from personal stock without cost.</t>
-        </is>
-      </c>
-      <c r="J321" t="inlineStr">
-        <is>
-          <t>Trigger Rate: 20% chance to use free recovery item at turn start
-Heroine: Monica</t>
-        </is>
-      </c>
+          <t>Heroine: Monica | 20% trigger rate at start of turn.
+Uses a free recovery item from personal stock without turn cost.</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr"/>
       <c r="K321" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16351,15 +16319,11 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>Decrease turn delay after using skills or magic.</t>
-        </is>
-      </c>
-      <c r="J322" t="inlineStr">
-        <is>
-          <t>Action Delay Reduction: -20% recovery delay after any action
-Heroine: Alisia</t>
-        </is>
-      </c>
+          <t>Heroine: Alisia | Action Recovery Acceleration.
+Decreases action recovery delay by 20% after using skills or magic.</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr"/>
       <c r="K322" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16405,15 +16369,11 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>Increased potency and effectiveness for all maid skills.</t>
-        </is>
-      </c>
-      <c r="J323" t="inlineStr">
-        <is>
-          <t>Maid Skill Potency: +15% effectiveness to First Aid, Cook, etc.
-Heroine: Conette</t>
-        </is>
-      </c>
+          <t>Heroine: Conette | Maid Mastery Booster.
+Increases potency and effectiveness of all Maid skills by +15%.</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr"/>
       <c r="K323" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16459,15 +16419,11 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>May occasionally act twice in one turn.</t>
-        </is>
-      </c>
-      <c r="J324" t="inlineStr">
-        <is>
-          <t>Double Action Rate: 15% chance to receive an extra turn immediately
-Heroine: Yuni</t>
-        </is>
-      </c>
+          <t>Heroine: Yuni | 15% double action chance.
+Grants an immediate second action in the same turn.</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16513,15 +16469,11 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>If killed in battle, revive after 3 turns.</t>
-        </is>
-      </c>
-      <c r="J325" t="inlineStr">
-        <is>
-          <t>Auto-Revive: Resurrects with 50% HP after 3 combat turns
-Heroine: Gina</t>
-        </is>
-      </c>
+          <t>Heroine: Gina | Auto-Resurrection.
+Resurrects with 50% Max HP 3 turns after falling in combat.</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16567,15 +16519,11 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>Whole row takes less damage from Demons, Undead, and Apparitions.</t>
-        </is>
-      </c>
-      <c r="J326" t="inlineStr">
-        <is>
-          <t>Row Damage Mitigation: -20% incoming damage from specified monster types
-Heroine: Ist</t>
-        </is>
-      </c>
+          <t>Heroine: Ist | Row Protection Barrier.
+Reduces incoming damage from Demons, Undead, and Apparitions by 20%.</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16621,15 +16569,11 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>May lower all enemies' ATK and INT at start of turn.</t>
-        </is>
-      </c>
-      <c r="J327" t="inlineStr">
-        <is>
-          <t>Trigger Rate: 15% at turn start    |    Inflicts -20% ATK and -20% INT
-Heroine: Fiora</t>
-        </is>
-      </c>
+          <t>Heroine: Fiora | 15% trigger rate at start of turn.
+Inflicts -20% ATK and -20% INT on all enemies.</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16675,15 +16619,11 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>Magic will occasionally activate immediately without chanting.</t>
-        </is>
-      </c>
-      <c r="J328" t="inlineStr">
-        <is>
-          <t>Instant Cast Rate: 15% chance for cast spells to trigger with 0 chant time
-Heroine: Eltricia</t>
-        </is>
-      </c>
+          <t>Heroine: Eltricia | 15% instant cast chance.
+Offensive and support spells activate immediately with 0 chant time.</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16729,15 +16669,11 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>Occasionally reflects incoming damage back as fixed neutral damage.</t>
-        </is>
-      </c>
-      <c r="J329" t="inlineStr">
-        <is>
-          <t>Reflect Rate: 20% chance to reflect 30% of received damage to attacker
-Heroine: Melvy</t>
-        </is>
-      </c>
+          <t>Heroine: Melvy | 20% damage reflect rate.
+Reflects 30% of received damage back to attacker as neutral damage.</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr"/>
       <c r="K329" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16783,15 +16719,11 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>Summons a shadow clone on normal attacks to deliver an extra strike.</t>
-        </is>
-      </c>
-      <c r="J330" t="inlineStr">
-        <is>
-          <t>Shadow Strike: Normal attacks trigger an extra hit dealing 75% damage
-Heroine: Tsurara</t>
-        </is>
-      </c>
+          <t>Heroine: Tsurara | Shadow Clone Follow-up.
+Normal attacks trigger an extra strike dealing 75% damage.</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16837,15 +16769,11 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>Increased effects for all class modifiers and masteries.</t>
-        </is>
-      </c>
-      <c r="J331" t="inlineStr">
-        <is>
-          <t>Class Stat Potency: +10% to all class stat bonuses and weapon masteries
-Heroine: Siena</t>
-        </is>
-      </c>
+          <t>Heroine: Siena | Class Mastery Booster.
+Increases all class stat bonuses and weapon masteries by +10%.</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr"/>
       <c r="K331" t="inlineStr">
         <is>
           <t>Approved</t>

--- a/mod_project/data_tables/skills.xlsx
+++ b/mod_project/data_tables/skills.xlsx
@@ -1025,9 +1025,20 @@
 Paralysis rate UP TP Cost UP</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Katana skill. Deal bash damage to one enemy. May paralyze.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ATK: 120% -&gt; 180% (+15%/Lv) | Paralysis: 25% -&gt; 50% (+6.25%/Lv)
+TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1069,9 +1080,20 @@
 Duration UP TP Cost UP Enemy critical rate UP</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Greatly boost own critical rate, but increase vulnerability to crits.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Crit Rate: +25% -&gt; +55% (+7.5%/Lv) | Enemy Crit: +15% -&gt; +25%
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -2133,9 +2155,20 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Sword and lance skill. Pierces through to the back row.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ATK: 135% -&gt; 195% (+15%/Lv) | Hits front and back target
+TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -2535,9 +2568,20 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Cure status ailments for a single ally.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Cures: Poison (L1) -&gt; Paralyze -&gt; Silence -&gt; Freeze -&gt; Sleep
+TP Cost: 3 -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 11 (L1-5)</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -2699,9 +2743,20 @@
 Duration UP TP Cost UP</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Increase own physical evasion and magic evasion.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Physical &amp; Magic EVA: +12% -&gt; +28% (+4%/Lv) | Levels: L1-5
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -3283,9 +3338,20 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Bow skill. Deal stab damage to one enemy. May slow.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>ATK: 115% -&gt; 175% (+15%/Lv) | Slow: 25% -&gt; 50% (+6.25%/Lv)
+TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -3551,9 +3617,20 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Deal bash damage to one enemy. May stun.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>ATK: 130% -&gt; 190% (+15%/Lv) | Stun: 30% -&gt; 60% (+7.5%/Lv)
+TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -3594,9 +3671,20 @@
           <t>LvUp: Identification success rate UP TP Cost DOWN</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Identify unknown dungeon loot items.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Success Rate: 70% -&gt; 98% (+7%/Lv) | Levels: L1-5
+TP Cost: 5 -&gt; 4 -&gt; 3 -&gt; 2 -&gt; 1 (Max)</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -3682,9 +3770,20 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Mace skill. Heavy bash strike with boosted accuracy.</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>ATK: 140% -&gt; 200% (+15%/Lv) | Accuracy: +25% -&gt; +45% (+5%/Lv)
+TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -3726,9 +3825,20 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Mace skill. Strike target and reduce enemy physical DEF by 10%.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>ATK: 125% -&gt; 185% (+15%/Lv) | Inflicts -10% DEF debuff
+TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 | Fast turn recovery (0.85x delay)</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -3770,9 +3880,20 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Sword skill. Deal slash damage to all enemies on screen.</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>ATK: 120% -&gt; 160% (+10%/Lv, L1-5) | Hits all foes
+TP Cost: 36 -&gt; 46 -&gt; 57 -&gt; 68 -&gt; 79 | Action delay: 0.80x -&gt; 0.98x</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -3858,9 +3979,20 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Transform into Magical Princess, raising all stats.</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>All Stats: +15% -&gt; +35% (+5%/Lv) | Levels: L1-5
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -3902,9 +4034,20 @@
 Time until next turn DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Short-range strike dealing heavy lightning damage to one enemy.</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>ATK: 136% -&gt; 216% (+20%/Lv, L1-5) | Lightning element
+TP Cost: 13 -&gt; 20 -&gt; 28 -&gt; 36 -&gt; 45</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -4307,9 +4450,20 @@
           <t>LvUp: TP recovery UP</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Focus divine power to restore own TP.</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>TP Restore: 16% -&gt; 25% Max TP (+2.25%/Lv) | Levels: L1-5
+TP Cost: 0 | Action delay: 1.00x</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -4350,9 +4504,20 @@
           <t>LvUp: ATK decrease UP</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Dance skill. Lower all enemies' physical ATK while dance lasts.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Enemy ATK: -12% -&gt; -24% (-3%/Lv) | Levels: L1-5
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -4393,9 +4558,20 @@
           <t>LvUp: DEF decrease UP</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Dance skill. Lower all enemies' physical DEF while dance lasts.</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Enemy DEF: -12% -&gt; -24% (-3%/Lv) | Levels: L1-5
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -4653,9 +4829,20 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Whip skill. Deal bash damage to an enemy row from mid-range.</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>ATK: 120% -&gt; 180% (+15%/Lv) | Row bash attack
+TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 (L1-5)</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -4943,9 +5130,20 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Attack one enemy. May instakill.</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>ATK: 140% -&gt; 200% (+15%/Lv) | Instakill Chance: 15% -&gt; 35% (+5%/Lv)
+TP Cost: 16 -&gt; 19 -&gt; 22 -&gt; 25 -&gt; 28 (L1-5)</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -5031,9 +5229,20 @@
 Time until next turn DOWN TP Cost UP DEF decrease UP</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Greatly boost own physical ATK at the cost of reducing DEF to 0.</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>ATK: +40% -&gt; +80% (+10%/Lv) | User DEF reduced to 0
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -5201,9 +5410,20 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Fan skill. Deal bash damage to one enemy and delay target turn.</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>ATK: 120% -&gt; 180% (+15%/Lv) | Action Delay: -20% -&gt; -40%
+TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -5371,9 +5591,20 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Convert current DEF to bonus ATK (user DEF becomes 0).</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>ATK Bonus: 100% -&gt; 150% of converted DEF value (+12.5%/Lv)
+Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 | TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -5497,9 +5728,20 @@
 Time until next turn DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Summon puppet Spartan to attack enemies with short-range bash strikes.</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Puppet Power: 100% -&gt; 160% (+15%/Lv) | Duration: 4 -&gt; 6 turns
+TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 (L1-5)</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -5585,9 +5827,20 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Summon puppet Catalina to heal party members' HP.</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Heal Potency: 20% -&gt; 40% Max HP (+5%/Lv) | Duration: 4 -&gt; 6 turns
+TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 (L1-5)</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -5673,9 +5926,20 @@
 petrify &gt; slow &gt; all debuffs TP Cost UP</t>
         </is>
       </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Summon puppet Perdurabo to cure allies' status ailments.</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Cures status ailments for 2 allies per turn | Duration: 4 -&gt; 6 turns
+TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 (L1-5)</t>
+        </is>
+      </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -5717,9 +5981,20 @@
 Time until next turn DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Summon puppet Musiy to cast immediate single-target attack spells.</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Spell Pwr: 120 -&gt; 240 (+30/Lv) | Duration: 4 -&gt; 6 turns
+TP Cost: 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 (L1-5)</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -7669,9 +7944,20 @@
 TP Cost UP Chant time UP</t>
         </is>
       </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Deal fire damage to an enemy row.</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Pwr (L1-10): 90 -&gt; 125 -&gt; 160 -&gt; 200 -&gt; 250 -&gt; 300 -&gt; 360 -&gt; 420 -&gt; 480 -&gt; 530
+TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 43 -&gt; 49 -&gt; 55 -&gt; 60 (Lv1 to Max)</t>
+        </is>
+      </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -7713,9 +7999,20 @@
 TP Cost UP Chant time UP</t>
         </is>
       </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Deal fire damage to all enemies.</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Pwr (L1-10): 80 -&gt; 110 -&gt; 140 -&gt; 180 -&gt; 230 -&gt; 280 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 510
+TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 41 -&gt; 48 -&gt; 55 -&gt; 63 -&gt; 71 -&gt; 79 -&gt; 88 (Lv1 to Max)</t>
+        </is>
+      </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -7757,9 +8054,20 @@
 TP Cost UP Chant time UP</t>
         </is>
       </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Unleash devastating master fire magic on one enemy.</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Pwr (L1-10): 620 -&gt; 680 -&gt; 750 -&gt; 830 -&gt; 920 -&gt; 1010 -&gt; 1100 -&gt; 1200 -&gt; 1250 -&gt; 1300
+TP Cost: 40 -&gt; 44 -&gt; 48 -&gt; 53 -&gt; 58 -&gt; 64 -&gt; 70 -&gt; 76 -&gt; 80 -&gt; 84 (Lv1 to Max)</t>
+        </is>
+      </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -7801,9 +8109,20 @@
 TP Cost UP Chant time UP</t>
         </is>
       </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Deal water damage to one enemy.</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Pwr (L1-10): 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520
+TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32 (Lv1 to Max)</t>
+        </is>
+      </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -7845,9 +8164,20 @@
 TP Cost UP Chant time UP</t>
         </is>
       </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Deal water damage to an enemy row.</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Pwr (L1-10): 90 -&gt; 125 -&gt; 160 -&gt; 200 -&gt; 250 -&gt; 300 -&gt; 360 -&gt; 420 -&gt; 480 -&gt; 530
+TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 43 -&gt; 49 -&gt; 55 -&gt; 60 (Lv1 to Max)</t>
+        </is>
+      </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -7889,9 +8219,20 @@
 TP Cost UP Chant time UP</t>
         </is>
       </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Deal water damage to all enemies.</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Pwr (L1-10): 80 -&gt; 110 -&gt; 140 -&gt; 180 -&gt; 230 -&gt; 280 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 510
+TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 41 -&gt; 48 -&gt; 55 -&gt; 63 -&gt; 71 -&gt; 79 -&gt; 88 (Lv1 to Max)</t>
+        </is>
+      </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -7933,9 +8274,20 @@
 TP Cost UP Chant time UP</t>
         </is>
       </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Unleash devastating master water magic on one enemy.</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Pwr (L1-10): 620 -&gt; 680 -&gt; 750 -&gt; 830 -&gt; 920 -&gt; 1010 -&gt; 1100 -&gt; 1200 -&gt; 1250 -&gt; 1300
+TP Cost: 40 -&gt; 44 -&gt; 48 -&gt; 53 -&gt; 58 -&gt; 64 -&gt; 70 -&gt; 76 -&gt; 80 -&gt; 84 (Lv1 to Max)</t>
+        </is>
+      </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -8037,9 +8389,20 @@
 TP Cost UP Chant time UP</t>
         </is>
       </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Deal lightning damage to an enemy row.</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Pwr (L1-10): 90 -&gt; 125 -&gt; 160 -&gt; 200 -&gt; 250 -&gt; 300 -&gt; 360 -&gt; 420 -&gt; 480 -&gt; 530
+TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 43 -&gt; 49 -&gt; 55 -&gt; 60 (Lv1 to Max)</t>
+        </is>
+      </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -8081,9 +8444,20 @@
 TP Cost UP Chant time UP</t>
         </is>
       </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Deal lightning damage to all enemies.</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Pwr (L1-10): 80 -&gt; 110 -&gt; 140 -&gt; 180 -&gt; 230 -&gt; 280 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 510
+TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 41 -&gt; 48 -&gt; 55 -&gt; 63 -&gt; 71 -&gt; 79 -&gt; 88 (Lv1 to Max)</t>
+        </is>
+      </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -8125,9 +8499,20 @@
 TP Cost UP Chant time UP</t>
         </is>
       </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Unleash devastating master lightning magic on one enemy.</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Pwr (L1-10): 620 -&gt; 680 -&gt; 750 -&gt; 830 -&gt; 920 -&gt; 1010 -&gt; 1100 -&gt; 1200 -&gt; 1250 -&gt; 1300
+TP Cost: 40 -&gt; 44 -&gt; 48 -&gt; 53 -&gt; 58 -&gt; 64 -&gt; 70 -&gt; 76 -&gt; 80 -&gt; 84 (Lv1 to Max)</t>
+        </is>
+      </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -8229,9 +8614,20 @@
 TP Cost UP Chant time UP</t>
         </is>
       </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Deal wind damage to an enemy row.</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Pwr (L1-10): 90 -&gt; 125 -&gt; 160 -&gt; 200 -&gt; 250 -&gt; 300 -&gt; 360 -&gt; 420 -&gt; 480 -&gt; 530
+TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 43 -&gt; 49 -&gt; 55 -&gt; 60 (Lv1 to Max)</t>
+        </is>
+      </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -8273,9 +8669,20 @@
 TP Cost UP Chant time UP</t>
         </is>
       </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Deal wind damage to all enemies.</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Pwr (L1-10): 80 -&gt; 110 -&gt; 140 -&gt; 180 -&gt; 230 -&gt; 280 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 510
+TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 41 -&gt; 48 -&gt; 55 -&gt; 63 -&gt; 71 -&gt; 79 -&gt; 88 (Lv1 to Max)</t>
+        </is>
+      </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -8317,9 +8724,20 @@
 TP Cost UP Chant time UP</t>
         </is>
       </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Unleash devastating master wind magic on one enemy.</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Pwr (L1-10): 620 -&gt; 680 -&gt; 750 -&gt; 830 -&gt; 920 -&gt; 1010 -&gt; 1100 -&gt; 1200 -&gt; 1250 -&gt; 1300
+TP Cost: 40 -&gt; 44 -&gt; 48 -&gt; 53 -&gt; 58 -&gt; 64 -&gt; 70 -&gt; 76 -&gt; 80 -&gt; 84 (Lv1 to Max)</t>
+        </is>
+      </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -8421,9 +8839,20 @@
 TP Cost UP Chant time UP</t>
         </is>
       </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Deal earth damage to an enemy row.</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Pwr (L1-10): 90 -&gt; 125 -&gt; 160 -&gt; 200 -&gt; 250 -&gt; 300 -&gt; 360 -&gt; 420 -&gt; 480 -&gt; 530
+TP Cost: 15 -&gt; 19 -&gt; 23 -&gt; 27 -&gt; 32 -&gt; 37 -&gt; 43 -&gt; 49 -&gt; 55 -&gt; 60 (Lv1 to Max)</t>
+        </is>
+      </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -8465,9 +8894,20 @@
 TP Cost UP Chant time UP</t>
         </is>
       </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Deal earth damage to all enemies.</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Pwr (L1-10): 80 -&gt; 110 -&gt; 140 -&gt; 180 -&gt; 230 -&gt; 280 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 510
+TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 41 -&gt; 48 -&gt; 55 -&gt; 63 -&gt; 71 -&gt; 79 -&gt; 88 (Lv1 to Max)</t>
+        </is>
+      </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -8509,9 +8949,20 @@
 TP Cost UP Chant time UP</t>
         </is>
       </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Unleash devastating master earth magic on one enemy.</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Pwr (L1-10): 620 -&gt; 680 -&gt; 750 -&gt; 830 -&gt; 920 -&gt; 1010 -&gt; 1100 -&gt; 1200 -&gt; 1250 -&gt; 1300
+TP Cost: 40 -&gt; 44 -&gt; 48 -&gt; 53 -&gt; 58 -&gt; 64 -&gt; 70 -&gt; 76 -&gt; 80 -&gt; 84 (Lv1 to Max)</t>
+        </is>
+      </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -8553,9 +9004,20 @@
 TP Cost UP Chant time UP</t>
         </is>
       </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Neutral magic strike to one enemy. Absorb damage dealt as HP.</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Pwr: 60 -&gt; 120 -&gt; 180 -&gt; 260 -&gt; 350 (L1-5) | Bypasses elemental resists
+TP Cost: 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 18</t>
+        </is>
+      </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -8597,9 +9059,20 @@
 TP Cost UP Chant time UP</t>
         </is>
       </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Neutral magic strike to one enemy. Absorb damage dealt as TP.</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Pwr: 22 -&gt; 35 -&gt; 50 -&gt; 65 -&gt; 82 (L1-5) | Restores TP equal to damage dealt
+TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 15</t>
+        </is>
+      </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -8641,9 +9114,20 @@
 Duration UP TP Cost UP</t>
         </is>
       </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Boost own magic attack power at the cost of consuming HP.</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Magic ATK: +20% -&gt; +40% (+5%/Lv) | HP Cost: 10% Max HP
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
+        </is>
+      </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -8685,9 +9169,20 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Transfer a portion of user HP to restore an ally's HP.</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Heal: 30% -&gt; 60% (+7.5%/Lv) of target Max HP | Consumes 20% user HP
+TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 (L1-5)</t>
+        </is>
+      </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -8729,9 +9224,20 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Deal magic damage to one enemy. May stun.</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Stun Chance: 30% -&gt; 60% (+7.5%/Lv) | Levels: L1-5
+TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
+        </is>
+      </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -8773,9 +9279,20 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Poison all enemies (5% Max HP damage per enemy turn, cap 250).</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Accuracy: +15% -&gt; +35% (+5%/Lv) | Chant: 1.20x -&gt; 1.40x
+TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5)</t>
+        </is>
+      </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -8817,9 +9334,20 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Deal water magic damage to one enemy. May freeze.</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Freeze Chance: 30% -&gt; 60% (+7.5%/Lv) | Levels: L1-5
+TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
+        </is>
+      </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -8861,9 +9389,20 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Deal lightning magic damage to one enemy. May paralyze.</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Paralysis Chance: 30% -&gt; 60% (+7.5%/Lv) | Levels: L1-5
+TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
+        </is>
+      </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -8905,9 +9444,20 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Put an enemy to sleep with magic.</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Sleep Chance: 40% -&gt; 70% (+7.5%/Lv) | Levels: L1-5
+TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
+        </is>
+      </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -8949,9 +9499,20 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Silence an enemy to prevent spell casting.</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Silence Chance: 40% -&gt; 70% (+7.5%/Lv) | Levels: L1-5
+TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
+        </is>
+      </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -8993,9 +9554,20 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Turn one enemy to stone with earth magic.</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Petrify Chance: 20% -&gt; 40% (+5%/Lv) | Levels: L1-5
+TP Cost: 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 22</t>
+        </is>
+      </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -9037,9 +9609,20 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Attempt to instantly slay one living enemy.</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Instakill Chance: 15% -&gt; 35% (+5%/Lv) | Levels: L1-5
+TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 28</t>
+        </is>
+      </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -9081,9 +9664,20 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Inflict Slow on an enemy row, cutting action speed by -50%.</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Slow Chance: 35% -&gt; 65% (+7.5%/Lv) | Inflicts -50% Speed
+TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 (L1-5)</t>
+        </is>
+      </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -9125,9 +9719,20 @@
 TP Cost UP</t>
         </is>
       </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Terrify an enemy with dark magic to inflict Stun.</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Stun Chance: 30% -&gt; 60% (+7.5%/Lv) | Levels: L1-5
+TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
+        </is>
+      </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -9257,9 +9862,20 @@
 Time until next turn DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Imbue an ally's weapon with Fire element.</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5) | Adds Fire damage to weapon strikes
+TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
+        </is>
+      </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -9301,9 +9917,20 @@
 Time until next turn DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Imbue an ally's weapon with Water element.</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5) | Adds Water damage to weapon strikes
+TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
+        </is>
+      </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -9345,9 +9972,20 @@
 Time until next turn DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Imbue an ally's weapon with Lightning element.</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5) | Adds Lightning damage to weapon strikes
+TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
+        </is>
+      </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -9389,9 +10027,20 @@
 Time until next turn DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Imbue an ally's weapon with Wind element.</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5) | Adds Wind damage to weapon strikes
+TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
+        </is>
+      </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -9433,9 +10082,20 @@
 Time until next turn DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Imbue an ally's weapon with Earth element.</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 (L1-5) | Adds Earth damage to weapon strikes
+TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
+        </is>
+      </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -9477,9 +10137,20 @@
 Time until next turn DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Raise one row of allies' resistance to stab damage.</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Stab Resistance: +15 -&gt; +35 (+5/Lv) | Levels: L1-5
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
+        </is>
+      </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -9521,9 +10192,20 @@
 Time until next turn DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Raise one row of allies' resistance to slash damage.</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Slash Resistance: +15 -&gt; +35 (+5/Lv) | Levels: L1-5
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
+        </is>
+      </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -9565,9 +10247,20 @@
 Time until next turn DOWN TP Cost UP</t>
         </is>
       </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Raise one row of allies' resistance to bash damage.</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Bash Resistance: +15 -&gt; +35 (+5/Lv) | Levels: L1-5
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18</t>
+        </is>
+      </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -14330,9 +15023,20 @@
           <t>LvUp: Activation rate UP</t>
         </is>
       </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Occasionally nullify physical damage.</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>Nullify Rate: 8% -&gt; 20% (+3%/Lv) | Levels: L1-5
+Completely negates incoming physical attacks when triggered</t>
+        </is>
+      </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -14373,9 +15077,20 @@
           <t>LvUp: Can cure poison &gt; paralysis &gt; silence &gt; freeze &gt; sleep &gt; slow</t>
         </is>
       </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Automatically cure own status ailments at start of turn.</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>Cures: Poison (L1) -&gt; Paralyze -&gt; Silence -&gt; Freeze -&gt; Sleep -&gt; Slow
+Triggers automatically at start of user's combat turn</t>
+        </is>
+      </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -14416,9 +15131,20 @@
           <t>LvUp: ATK/DEX increase UP</t>
         </is>
       </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Boost physical ATK and DEX when HP drops below 50%.</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>ATK &amp; DEX: +20% -&gt; +40% (+5%/Lv) when HP &lt; 50% | Levels: L1-5
+Immediate combat stat trigger</t>
+        </is>
+      </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -14636,9 +15362,20 @@
           <t>LvUp: Accuracy UP</t>
         </is>
       </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Heighten magic accuracy for all cast spells.</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>Magic Accuracy: +15% -&gt; +35% (+5%/Lv) | Levels: L1-5
+Significantly reduces spell evasion by high RES targets</t>
+        </is>
+      </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -14679,9 +15416,20 @@
           <t>LvUp: Enemy preemptive attack rate DOWN</t>
         </is>
       </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Reduce enemy preemptive strike rate in dungeons.</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>Preemptive Reduction: -20% -&gt; -60% (-10%/Lv) | Levels: L1-5
+Protects party from surprise enemy encounters</t>
+        </is>
+      </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -14722,9 +15470,20 @@
           <t>LvUp: Preemptive attack rate UP</t>
         </is>
       </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Increase party's preemptive strike rate against foes.</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>Party Preemptive Rate: +10% -&gt; +30% (+5%/Lv) | Levels: L1-5
+Grants free initial turn before enemies act</t>
+        </is>
+      </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -14765,9 +15524,20 @@
           <t>LvUp: Battle escape rate UP</t>
         </is>
       </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Increase success rate when attempting to flee from battle.</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>Escape Success: +20% -&gt; +50% (+7.5%/Lv) | Levels: L1-5
+Does not apply to scripted boss battles</t>
+        </is>
+      </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -14926,9 +15696,20 @@
           <t>LvUp: Found item quality UP</t>
         </is>
       </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Occasionally discover items while exploring dungeons.</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>Item Find Rate: +10% -&gt; +30% (+5%/Lv) | Levels: L1-5
+Finds consumables and crafting materials while walking</t>
+        </is>
+      </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -14969,9 +15750,20 @@
           <t>LvUp: Post-battle HP &amp; TP recovery UP</t>
         </is>
       </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Restore party HP and TP slightly after winning a battle.</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>Post-Battle Recovery: 5% -&gt; 15% HP &amp; TP (+2.5%/Lv) | Levels: L1-5
+Restores whole party after combat conclusion</t>
+        </is>
+      </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -15012,9 +15804,20 @@
           <t>LvUp: Item keep rate UP</t>
         </is>
       </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Occasionally retain disposable items after using them in combat.</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>Item Retain Chance: 15% -&gt; 35% (+5%/Lv) | Levels: L1-5
+Item is not consumed from inventory when triggered</t>
+        </is>
+      </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -15114,9 +15917,20 @@
           <t>LvUp: Speed UP</t>
         </is>
       </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>Become capable of performing two songs simultaneously.</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>Singing Speed: +10% -&gt; +30% (+5%/Lv) | Levels: L1-5
+Allows maintaining 2 active Bard songs at once</t>
+        </is>
+      </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -15157,9 +15971,20 @@
           <t>LvUp: Speed UP</t>
         </is>
       </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>Become capable of performing two dances simultaneously.</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>Dancing Speed: +10% -&gt; +30% (+5%/Lv) | Levels: L1-5
+Allows maintaining 2 active Dancer dances at once</t>
+        </is>
+      </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -15200,9 +16025,20 @@
           <t>LvUp: Speed UP</t>
         </is>
       </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Become capable of controlling two summoned dolls at once.</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>Doll Control Speed: +10% -&gt; +30% (+5%/Lv) | Levels: L1-5
+Maintains 2 active summoned dolls simultaneously</t>
+        </is>
+      </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -15243,9 +16079,20 @@
           <t>LvUp: Sealbook ability increase UP</t>
         </is>
       </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>Increase doll power with strength of equipped Sealbook.</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>Doll Power Bonus: +10% -&gt; +30% (+5%/Lv) based on Sealbook level
+Levels: L1-5</t>
+        </is>
+      </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -15463,9 +16310,20 @@
           <t>LvUp: Doll skill bonus UP</t>
         </is>
       </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>Increased potency and effectiveness for all doll skills.</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>Doll Stat Bonus: +3% -&gt; +15% (+3%/Lv) | Levels: L1-5
+Increases damage, healing, and durability of summoned dolls</t>
+        </is>
+      </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -15506,9 +16364,20 @@
           <t>LvUp: Double attack rate UP</t>
         </is>
       </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>Occasionally attack twice when performing normal attacks.</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>Double Attack Rate: 8% -&gt; 20% (+3%/Lv) | Levels: L1-5
+Normal attack trigger</t>
+        </is>
+      </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -15549,9 +16418,20 @@
           <t>LvUp: Song chant time DOWN</t>
         </is>
       </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>Reduce chant time required to start songs.</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>Song Chant Reduction: -10% -&gt; -30% (-5%/Lv) | Levels: L1-5
+Accelerates Bard song activation</t>
+        </is>
+      </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -15592,9 +16472,20 @@
           <t>LvUp: Negotiation rate UP</t>
         </is>
       </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>Reduce purchase and identification prices at shops.</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>Shop Discount: -5% -&gt; -25% (-5%/Lv) | Levels: L1-5
+Lowers gold cost for item purchases and item identification</t>
+        </is>
+      </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -15635,9 +16526,20 @@
           <t>LvUp: Occurrence rate UP</t>
         </is>
       </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>Mesmerize enemies with dance steps, causing them to lose turns.</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>Mesmerize Rate: 5% -&gt; 15% (+2.5%/Lv) | Levels: L1-5
+Enemy skips turn when mesmerized</t>
+        </is>
+      </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -15673,9 +16575,20 @@
           <t>Nullify first hit of battle against user (does not work for status ailments).</t>
         </is>
       </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>Nullify first hit of battle against user.</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>100% nullification of the very first physical attack received
+Fixed passive (Level 1)</t>
+        </is>
+      </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -15711,9 +16624,20 @@
           <t>Heighten the probability of beneficial results for random effect skills.</t>
         </is>
       </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>Heighten probability of beneficial results for random skills.</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>Drastically increases odds of favorable outcomes on Gamble skills
+Fixed passive (Level 1)</t>
+        </is>
+      </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -15879,9 +16803,20 @@
           <t>Increase doll summon duration by 1 turn.</t>
         </is>
       </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>Increase doll summon duration on battlefield.</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>Doll Summon Duration: +1 turn (Summons persist longer in battle)
+Fixed passive (Level 1)</t>
+        </is>
+      </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -15923,7 +16858,6 @@
 Effect: +1% damage per Pep point (up to +100% damage at Max Pep).</t>
         </is>
       </c>
-      <c r="J314" t="inlineStr"/>
       <c r="K314" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -15973,7 +16907,6 @@
 Inflicts Poison, Paralyze, Silence, or cancels enemy buffs.</t>
         </is>
       </c>
-      <c r="J315" t="inlineStr"/>
       <c r="K315" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16023,7 +16956,6 @@
 Inflicts Slow and -30% Speed on attacker.</t>
         </is>
       </c>
-      <c r="J316" t="inlineStr"/>
       <c r="K316" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16073,7 +17005,6 @@
 Grants +25% extra damage to all weapon-based techniques.</t>
         </is>
       </c>
-      <c r="J317" t="inlineStr"/>
       <c r="K317" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16123,7 +17054,6 @@
 Guarantees 100% hit rate and completely ignores target DEF.</t>
         </is>
       </c>
-      <c r="J318" t="inlineStr"/>
       <c r="K318" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16173,7 +17103,6 @@
 Chance to completely negate all incoming damage.</t>
         </is>
       </c>
-      <c r="J319" t="inlineStr"/>
       <c r="K319" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16223,7 +17152,6 @@
 Instantly eliminates enemy summon entities, puppets, and familiars.</t>
         </is>
       </c>
-      <c r="J320" t="inlineStr"/>
       <c r="K320" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16273,7 +17201,6 @@
 Uses a free recovery item from personal stock without turn cost.</t>
         </is>
       </c>
-      <c r="J321" t="inlineStr"/>
       <c r="K321" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16323,7 +17250,6 @@
 Decreases action recovery delay by 20% after using skills or magic.</t>
         </is>
       </c>
-      <c r="J322" t="inlineStr"/>
       <c r="K322" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16373,7 +17299,6 @@
 Increases potency and effectiveness of all Maid skills by +15%.</t>
         </is>
       </c>
-      <c r="J323" t="inlineStr"/>
       <c r="K323" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16423,7 +17348,6 @@
 Grants an immediate second action in the same turn.</t>
         </is>
       </c>
-      <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16473,7 +17397,6 @@
 Resurrects with 50% Max HP 3 turns after falling in combat.</t>
         </is>
       </c>
-      <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16523,7 +17446,6 @@
 Reduces incoming damage from Demons, Undead, and Apparitions by 20%.</t>
         </is>
       </c>
-      <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16573,7 +17495,6 @@
 Inflicts -20% ATK and -20% INT on all enemies.</t>
         </is>
       </c>
-      <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16623,7 +17544,6 @@
 Offensive and support spells activate immediately with 0 chant time.</t>
         </is>
       </c>
-      <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16673,7 +17593,6 @@
 Reflects 30% of received damage back to attacker as neutral damage.</t>
         </is>
       </c>
-      <c r="J329" t="inlineStr"/>
       <c r="K329" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16723,7 +17642,6 @@
 Normal attacks trigger an extra strike dealing 75% damage.</t>
         </is>
       </c>
-      <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -16773,7 +17691,6 @@
 Increases all class stat bonuses and weapon masteries by +10%.</t>
         </is>
       </c>
-      <c r="J331" t="inlineStr"/>
       <c r="K331" t="inlineStr">
         <is>
           <t>Approved</t>

--- a/mod_project/data_tables/skills.xlsx
+++ b/mod_project/data_tables/skills.xlsx
@@ -13884,9 +13884,25 @@
           <t>LvUp: HP recovery UP</t>
         </is>
       </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Slightly recover HP every turn during battle.</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>HP Regen (L1-5): 1% -&gt; 2% -&gt; 3% -&gt; 4% -&gt; 5% (+1%/Lv)
+Triggers at start of user's action in combat</t>
+        </is>
+      </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>QoL transparency: exact 1-5% per-turn HP regeneration scaling.</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/skills.xlsx
+++ b/mod_project/data_tables/skills.xlsx
@@ -16871,7 +16871,8 @@
       <c r="I314" t="inlineStr">
         <is>
           <t>Heroine: Luco | Damage scales with Pep.
-Effect: +1% damage per Pep point (up to +100% damage at Max Pep).</t>
+Effect: +1% damage per Pep point (up to +100% damage at Max Pep).
+[Crown EX]: Scales up to +150% damage bonus at Max Pep.</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
@@ -16920,7 +16921,8 @@
       <c r="I315" t="inlineStr">
         <is>
           <t>Heroine: Mefmera | 15% trigger chance on enemy action.
-Inflicts Poison, Paralyze, Silence, or cancels enemy buffs.</t>
+Inflicts Poison, Paralyze, Silence, or cancels enemy buffs.
+[Crown EX]: Trigger chance increases to 25% on any enemy action.</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
@@ -16969,7 +16971,8 @@
       <c r="I316" t="inlineStr">
         <is>
           <t>Heroine: Souffle | 25% counter chance on physical contact.
-Inflicts Slow and -30% Speed on attacker.</t>
+Inflicts Slow and -30% Speed on attacker.
+[Crown EX]: Counter chance increases to 40% on physical contact.</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
@@ -17018,7 +17021,8 @@
       <c r="I317" t="inlineStr">
         <is>
           <t>Heroine: Grishna | Weapon Scaling Bonus.
-Grants +25% extra damage to all weapon-based techniques.</t>
+Grants +25% extra damage to all weapon-based techniques.
+[Crown EX]: Weapon technique damage bonus increases to +40%.</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
@@ -17067,7 +17071,8 @@
       <c r="I318" t="inlineStr">
         <is>
           <t>Heroine: Yae | 20% activation rate on physical attacks.
-Guarantees 100% hit rate and completely ignores target DEF.</t>
+Guarantees 100% hit rate and completely ignores target DEF.
+[Crown EX]: Activation rate increases to 30% (ignores target DEF).</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
@@ -17116,7 +17121,8 @@
       <c r="I319" t="inlineStr">
         <is>
           <t>Heroine: Lize | 10% nullification rate.
-Chance to completely negate all incoming damage.</t>
+Chance to completely negate all incoming damage.
+[Crown EX]: Total damage nullification rate increases to 15%.</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -17165,7 +17171,8 @@
       <c r="I320" t="inlineStr">
         <is>
           <t>Heroine: Lilian | 25% banish rate before acting.
-Instantly eliminates enemy summon entities, puppets, and familiars.</t>
+Instantly eliminates enemy summon entities, puppets, and familiars.
+[Crown EX]: Enemy summon and minion banish rate increases to 40%.</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
@@ -17214,7 +17221,8 @@
       <c r="I321" t="inlineStr">
         <is>
           <t>Heroine: Monica | 20% trigger rate at start of turn.
-Uses a free recovery item from personal stock without turn cost.</t>
+Uses a free recovery item from personal stock without turn cost.
+[Crown EX]: Free item trigger rate increases to 30% without turn cost.</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
@@ -17263,7 +17271,8 @@
       <c r="I322" t="inlineStr">
         <is>
           <t>Heroine: Alisia | Action Recovery Acceleration.
-Decreases action recovery delay by 20% after using skills or magic.</t>
+Decreases action recovery delay by 20% after using skills or magic.
+[Crown EX]: Action recovery delay reduction increases to 30%.</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
@@ -17312,7 +17321,8 @@
       <c r="I323" t="inlineStr">
         <is>
           <t>Heroine: Conette | Maid Mastery Booster.
-Increases potency and effectiveness of all Maid skills by +15%.</t>
+Increases potency and effectiveness of all Maid skills by +15%.
+[Crown EX]: Maid skill effectiveness bonus increases to +25%.</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
@@ -17361,7 +17371,8 @@
       <c r="I324" t="inlineStr">
         <is>
           <t>Heroine: Yuni | 15% double action chance.
-Grants an immediate second action in the same turn.</t>
+Grants an immediate second action in the same turn.
+[Crown EX]: Immediate second action trigger rate increases to 25%.</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
@@ -17410,7 +17421,8 @@
       <c r="I325" t="inlineStr">
         <is>
           <t>Heroine: Gina | Auto-Resurrection.
-Resurrects with 50% Max HP 3 turns after falling in combat.</t>
+Resurrects with 50% Max HP 3 turns after falling in combat.
+[Crown EX]: Resurrects with 100% Max HP after 2 turns.</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
@@ -17459,7 +17471,8 @@
       <c r="I326" t="inlineStr">
         <is>
           <t>Heroine: Ist | Row Protection Barrier.
-Reduces incoming damage from Demons, Undead, and Apparitions by 20%.</t>
+Reduces incoming damage from Demons, Undead, and Apparitions by 20%.
+[Crown EX]: Damage reduction from Demons/Undead/Apparitions to 30%.</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -17508,7 +17521,8 @@
       <c r="I327" t="inlineStr">
         <is>
           <t>Heroine: Fiora | 15% trigger rate at start of turn.
-Inflicts -20% ATK and -20% INT on all enemies.</t>
+Inflicts -20% ATK and -20% INT on all enemies.
+[Crown EX]: Turn-start debuff trigger rate increases to 25%.</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
@@ -17557,7 +17571,8 @@
       <c r="I328" t="inlineStr">
         <is>
           <t>Heroine: Eltricia | 15% instant cast chance.
-Offensive and support spells activate immediately with 0 chant time.</t>
+Offensive and support spells activate immediately with 0 chant time.
+[Crown EX]: Instant cast (0 chant delay) rate increases to 25%.</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -17606,7 +17621,8 @@
       <c r="I329" t="inlineStr">
         <is>
           <t>Heroine: Melvy | 20% damage reflect rate.
-Reflects 30% of received damage back to attacker as neutral damage.</t>
+Reflects 30% of received damage back to attacker as neutral damage.
+[Crown EX]: Damage reflect rate increases to 30% with 45% reflected.</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
@@ -17655,7 +17671,8 @@
       <c r="I330" t="inlineStr">
         <is>
           <t>Heroine: Tsurara | Shadow Clone Follow-up.
-Normal attacks trigger an extra strike dealing 75% damage.</t>
+Normal attacks trigger an extra strike dealing 75% damage.
+[Crown EX]: Shadow strike follow-up deals 100% full attack damage.</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
@@ -17704,7 +17721,8 @@
       <c r="I331" t="inlineStr">
         <is>
           <t>Heroine: Siena | Class Mastery Booster.
-Increases all class stat bonuses and weapon masteries by +10%.</t>
+Increases all class stat bonuses and weapon masteries by +10%.
+[Crown EX]: Class and weapon mastery bonuses increase to +15%.</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">

--- a/mod_project/data_tables/skills.xlsx
+++ b/mod_project/data_tables/skills.xlsx
@@ -8056,7 +8056,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Unleash devastating master fire magic on one enemy.</t>
+          <t>Unleash devastating master fire magic on one enemy. Pierces 50 Elemental Res.</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Unleash devastating master water magic on one enemy.</t>
+          <t>Unleash devastating master water magic on one enemy. Pierces 50 Elemental Res.</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Unleash devastating master lightning magic on one enemy.</t>
+          <t>Unleash devastating master lightning magic on one enemy. Pierces 50 Elemental Res.</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Unleash devastating master wind magic on one enemy.</t>
+          <t>Unleash devastating master wind magic on one enemy. Pierces 50 Elemental Res.</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Unleash devastating master earth magic on one enemy.</t>
+          <t>Unleash devastating master earth magic on one enemy. Pierces 50 Elemental Res.</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -15208,8 +15208,7 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>Interruption Resist: +20% -&gt; +50% (+7.5%/Lv) | Levels: L1-5
-Crucial for casters and performers in front row</t>
+          <t>Interruption Resist: +20% -&gt; +50% (+7.5%/Lv) | 80% Crit Interrupt Res at Lv 5</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -16043,7 +16042,7 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>Become capable of controlling two summoned dolls at once.</t>
+          <t>Become capable of controlling two summoned dolls at once. Dolls gain Guts.</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
